--- a/Marielle - Model training results.xlsx
+++ b/Marielle - Model training results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="86" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
   <si>
     <t>Features</t>
   </si>
@@ -127,9 +127,6 @@
        'AIModelsChoice', 'AISelect', 'AIAgents', 'Country', 'EdLevel',
        'DevType', 'OrgSize', 'ICorPM', 'RemoteWork', 'Industry', 'Employment',
        'LanguageHaveWorkedWith_count']</t>
-  </si>
-  <si>
-    <t xml:space="preserve">  </t>
   </si>
   <si>
     <r>
@@ -1688,8 +1685,8 @@
       <c r="I32" s="42">
         <v>26131.1482578102</v>
       </c>
-      <c r="J32" s="44" t="s">
-        <v>30</v>
+      <c r="J32" s="44">
+        <v>0.429144697791336</v>
       </c>
     </row>
     <row r="33" ht="15.75" customHeight="1">
@@ -1831,7 +1828,7 @@
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="18"/>
       <c r="B38" s="34" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="C38" s="48">
         <v>30995.6855208029</v>
@@ -4784,13 +4781,13 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="2" t="s">
         <v>33</v>
-      </c>
-      <c r="C1" s="2" t="s">
-        <v>34</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -4798,10 +4795,10 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
+        <v>34</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>35</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>36</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -4809,10 +4806,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
+        <v>36</v>
+      </c>
+      <c r="C3" s="6" t="s">
         <v>37</v>
-      </c>
-      <c r="C3" s="6" t="s">
-        <v>38</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -4820,10 +4817,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="C4" s="6" t="s">
         <v>39</v>
-      </c>
-      <c r="C4" s="6" t="s">
-        <v>40</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -4831,10 +4828,10 @@
         <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
+        <v>40</v>
+      </c>
+      <c r="C5" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C5" s="6" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -4842,10 +4839,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
+        <v>42</v>
+      </c>
+      <c r="C6" s="6" t="s">
         <v>43</v>
-      </c>
-      <c r="C6" s="6" t="s">
-        <v>44</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -4853,10 +4850,10 @@
         <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="C7" s="6" t="s">
         <v>45</v>
-      </c>
-      <c r="C7" s="6" t="s">
-        <v>46</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
@@ -4866,28 +4863,28 @@
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="B9" s="50"/>
       <c r="C9" s="50"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="B10" s="50"/>
       <c r="C10" s="50"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B11" s="50"/>
       <c r="C11" s="50"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="B12" s="50"/>
       <c r="C12" s="50"/>

--- a/Marielle - Model training results.xlsx
+++ b/Marielle - Model training results.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="94" uniqueCount="53">
   <si>
     <t>Features</t>
   </si>
@@ -150,6 +150,15 @@
       </rPr>
       <t>)</t>
     </r>
+  </si>
+  <si>
+    <t>10 Features</t>
+  </si>
+  <si>
+    <t>['WorkExp', 'ToolCountWork', 'ToolCountPersonal', 'Country', 'EdLevel', 'DevType', 'OrgSize', 'ICorPM', 'RemoteWork', 'Employment']</t>
+  </si>
+  <si>
+    <t>HuberRegressor(epsilon=1.35,max_iter=5000)</t>
   </si>
   <si>
     <t>Models</t>
@@ -382,7 +391,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="55">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -477,10 +486,16 @@
     <xf borderId="8" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf borderId="4" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1">
+      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+    </xf>
     <xf borderId="4" fillId="0" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="4" fillId="2" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
+      <alignment horizontal="right" readingOrder="0"/>
+    </xf>
+    <xf borderId="4" fillId="3" fontId="3" numFmtId="164" xfId="0" applyAlignment="1" applyBorder="1" applyFont="1" applyNumberFormat="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
@@ -1827,2157 +1842,2284 @@
     </row>
     <row r="38" ht="15.75" customHeight="1">
       <c r="A38" s="18"/>
-      <c r="B38" s="34" t="s">
+      <c r="B38" s="48" t="s">
         <v>30</v>
       </c>
-      <c r="C38" s="48">
+      <c r="C38" s="49">
         <v>30995.6855208029</v>
       </c>
-      <c r="D38" s="48">
+      <c r="D38" s="49">
         <v>1.78441354326218E11</v>
       </c>
-      <c r="E38" s="48">
+      <c r="E38" s="49">
         <v>422423.193404692</v>
       </c>
-      <c r="F38" s="49">
+      <c r="F38" s="50">
         <v>0.332325458248952</v>
       </c>
-      <c r="G38" s="48">
+      <c r="G38" s="49">
         <v>17977.8598259361</v>
       </c>
-      <c r="H38" s="48">
+      <c r="H38" s="49">
         <v>6.06965945998676E8</v>
       </c>
-      <c r="I38" s="48">
+      <c r="I38" s="49">
         <v>24636.6788751787</v>
       </c>
-      <c r="J38" s="49">
+      <c r="J38" s="50">
         <v>0.492573228206099</v>
       </c>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="B39" s="50"/>
-      <c r="C39" s="51"/>
-      <c r="D39" s="51"/>
-      <c r="E39" s="51"/>
-      <c r="F39" s="52"/>
-      <c r="G39" s="51"/>
-      <c r="H39" s="51"/>
-      <c r="I39" s="51"/>
-      <c r="J39" s="52"/>
+      <c r="A39" s="36" t="s">
+        <v>31</v>
+      </c>
+      <c r="B39" s="24" t="s">
+        <v>11</v>
+      </c>
+      <c r="C39" s="37">
+        <v>33791.7046087869</v>
+      </c>
+      <c r="D39" s="38">
+        <v>2.86889220322474E11</v>
+      </c>
+      <c r="E39" s="37">
+        <v>535620.406932441</v>
+      </c>
+      <c r="F39" s="39">
+        <v>0.324475070280771</v>
+      </c>
+      <c r="G39" s="38">
+        <v>17878.1821479555</v>
+      </c>
+      <c r="H39" s="37">
+        <v>5.89183262349789E8</v>
+      </c>
+      <c r="I39" s="37">
+        <v>24273.0975021687</v>
+      </c>
+      <c r="J39" s="40">
+        <v>0.507439646688507</v>
+      </c>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="B40" s="50"/>
-      <c r="C40" s="51"/>
-      <c r="D40" s="51"/>
-      <c r="E40" s="51"/>
-      <c r="F40" s="52"/>
-      <c r="G40" s="51"/>
-      <c r="H40" s="51"/>
-      <c r="I40" s="51"/>
-      <c r="J40" s="52"/>
+      <c r="A40" s="41" t="s">
+        <v>32</v>
+      </c>
+      <c r="B40" s="12" t="s">
+        <v>13</v>
+      </c>
+      <c r="C40" s="42">
+        <v>21854.3892736522</v>
+      </c>
+      <c r="D40" s="42">
+        <v>9.07920974523421E8</v>
+      </c>
+      <c r="E40" s="42">
+        <v>30131.7270418312</v>
+      </c>
+      <c r="F40" s="45">
+        <v>0.382749484700079</v>
+      </c>
+      <c r="G40" s="42">
+        <v>19699.2326874447</v>
+      </c>
+      <c r="H40" s="42">
+        <v>6.7012776010692E8</v>
+      </c>
+      <c r="I40" s="42">
+        <v>25886.8259952223</v>
+      </c>
+      <c r="J40" s="44">
+        <v>0.439769614354486</v>
+      </c>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="B41" s="50"/>
-      <c r="C41" s="51"/>
-      <c r="D41" s="51"/>
-      <c r="E41" s="51"/>
-      <c r="F41" s="52"/>
-      <c r="G41" s="51"/>
-      <c r="H41" s="51"/>
-      <c r="I41" s="51"/>
-      <c r="J41" s="52"/>
+      <c r="A41" s="14"/>
+      <c r="B41" s="6" t="s">
+        <v>14</v>
+      </c>
+      <c r="C41" s="42">
+        <v>22084.800112214</v>
+      </c>
+      <c r="D41" s="42">
+        <v>9.36915328544243E8</v>
+      </c>
+      <c r="E41" s="42">
+        <v>30609.0726508374</v>
+      </c>
+      <c r="F41" s="45">
+        <v>0.367843947468851</v>
+      </c>
+      <c r="G41" s="42">
+        <v>19921.8163769919</v>
+      </c>
+      <c r="H41" s="42">
+        <v>6.82505264314489E8</v>
+      </c>
+      <c r="I41" s="42">
+        <v>26124.8017086156</v>
+      </c>
+      <c r="J41" s="44">
+        <v>0.429421954746371</v>
+      </c>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="B42" s="50"/>
-      <c r="C42" s="51"/>
-      <c r="D42" s="51"/>
-      <c r="E42" s="51"/>
-      <c r="F42" s="52"/>
-      <c r="G42" s="51"/>
-      <c r="H42" s="51"/>
-      <c r="I42" s="51"/>
-      <c r="J42" s="52"/>
+      <c r="A42" s="14"/>
+      <c r="B42" s="15" t="s">
+        <v>15</v>
+      </c>
+      <c r="C42" s="42">
+        <v>70526.7744186693</v>
+      </c>
+      <c r="D42" s="46">
+        <v>3.9991561248624E12</v>
+      </c>
+      <c r="E42" s="42">
+        <v>1999789.02008747</v>
+      </c>
+      <c r="F42" s="44">
+        <v>0.201595074682693</v>
+      </c>
+      <c r="G42" s="42">
+        <v>20119.397019587</v>
+      </c>
+      <c r="H42" s="42">
+        <v>6.98722709340202E8</v>
+      </c>
+      <c r="I42" s="42">
+        <v>26433.3635646355</v>
+      </c>
+      <c r="J42" s="44">
+        <v>0.415864084110642</v>
+      </c>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="B43" s="50"/>
-      <c r="C43" s="51"/>
-      <c r="D43" s="51"/>
-      <c r="E43" s="51"/>
-      <c r="F43" s="52"/>
-      <c r="G43" s="51"/>
-      <c r="H43" s="51"/>
-      <c r="I43" s="51"/>
-      <c r="J43" s="52"/>
+      <c r="A43" s="14"/>
+      <c r="B43" s="6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C43" s="42">
+        <v>58102.0430009344</v>
+      </c>
+      <c r="D43" s="42">
+        <v>2.30760320282258E12</v>
+      </c>
+      <c r="E43" s="42">
+        <v>1519079.72233934</v>
+      </c>
+      <c r="F43" s="44">
+        <v>0.249390852308509</v>
+      </c>
+      <c r="G43" s="42">
+        <v>19145.0058876221</v>
+      </c>
+      <c r="H43" s="42">
+        <v>6.50854323443081E8</v>
+      </c>
+      <c r="I43" s="42">
+        <v>25511.8467274143</v>
+      </c>
+      <c r="J43" s="44">
+        <v>0.455882310317379</v>
+      </c>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="B44" s="50"/>
-      <c r="C44" s="51"/>
-      <c r="D44" s="51"/>
-      <c r="E44" s="51"/>
-      <c r="F44" s="52"/>
-      <c r="G44" s="51"/>
-      <c r="H44" s="51"/>
-      <c r="I44" s="51"/>
-      <c r="J44" s="52"/>
+      <c r="A44" s="14"/>
+      <c r="B44" s="6" t="s">
+        <v>18</v>
+      </c>
+      <c r="C44" s="42">
+        <v>34379.3840475352</v>
+      </c>
+      <c r="D44" s="42">
+        <v>3.1670574780769E11</v>
+      </c>
+      <c r="E44" s="42">
+        <v>562766.15730487</v>
+      </c>
+      <c r="F44" s="44">
+        <v>0.325955116318673</v>
+      </c>
+      <c r="G44" s="42">
+        <v>17854.3339640262</v>
+      </c>
+      <c r="H44" s="42">
+        <v>5.89045963926243E8</v>
+      </c>
+      <c r="I44" s="42">
+        <v>24270.2691358427</v>
+      </c>
+      <c r="J44" s="43">
+        <v>0.507554428903707</v>
+      </c>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="B45" s="50"/>
-      <c r="C45" s="51"/>
-      <c r="D45" s="51"/>
-      <c r="E45" s="51"/>
-      <c r="F45" s="52"/>
-      <c r="G45" s="51"/>
-      <c r="H45" s="51"/>
-      <c r="I45" s="51"/>
-      <c r="J45" s="52"/>
+      <c r="A45" s="18"/>
+      <c r="B45" s="48" t="s">
+        <v>33</v>
+      </c>
+      <c r="C45" s="49">
+        <v>21732.2295373333</v>
+      </c>
+      <c r="D45" s="49">
+        <v>1.77710427501928E9</v>
+      </c>
+      <c r="E45" s="49">
+        <v>42155.7146187712</v>
+      </c>
+      <c r="F45" s="51">
+        <v>0.398015973893902</v>
+      </c>
+      <c r="G45" s="49">
+        <v>17996.8319713964</v>
+      </c>
+      <c r="H45" s="49">
+        <v>5.99939649166267E8</v>
+      </c>
+      <c r="I45" s="49">
+        <v>24493.6654906175</v>
+      </c>
+      <c r="J45" s="50">
+        <v>0.498447249875418</v>
+      </c>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="B46" s="50"/>
-      <c r="C46" s="51"/>
-      <c r="D46" s="51"/>
-      <c r="E46" s="51"/>
-      <c r="F46" s="52"/>
-      <c r="G46" s="51"/>
-      <c r="H46" s="51"/>
-      <c r="I46" s="51"/>
-      <c r="J46" s="52"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="53"/>
+      <c r="D46" s="53"/>
+      <c r="E46" s="53"/>
+      <c r="F46" s="54"/>
+      <c r="G46" s="53"/>
+      <c r="H46" s="53"/>
+      <c r="I46" s="53"/>
+      <c r="J46" s="54"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="B47" s="50"/>
-      <c r="C47" s="51"/>
-      <c r="D47" s="51"/>
-      <c r="E47" s="51"/>
-      <c r="F47" s="52"/>
-      <c r="G47" s="51"/>
-      <c r="H47" s="51"/>
-      <c r="I47" s="51"/>
-      <c r="J47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="53"/>
+      <c r="D47" s="53"/>
+      <c r="E47" s="53"/>
+      <c r="F47" s="54"/>
+      <c r="G47" s="53"/>
+      <c r="H47" s="53"/>
+      <c r="I47" s="53"/>
+      <c r="J47" s="54"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="B48" s="50"/>
-      <c r="C48" s="51"/>
-      <c r="D48" s="51"/>
-      <c r="E48" s="51"/>
-      <c r="F48" s="52"/>
-      <c r="G48" s="51"/>
-      <c r="H48" s="51"/>
-      <c r="I48" s="51"/>
-      <c r="J48" s="52"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="53"/>
+      <c r="D48" s="53"/>
+      <c r="E48" s="53"/>
+      <c r="F48" s="54"/>
+      <c r="G48" s="53"/>
+      <c r="H48" s="53"/>
+      <c r="I48" s="53"/>
+      <c r="J48" s="54"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="B49" s="50"/>
-      <c r="C49" s="51"/>
-      <c r="D49" s="51"/>
-      <c r="E49" s="51"/>
-      <c r="F49" s="52"/>
-      <c r="G49" s="51"/>
-      <c r="H49" s="51"/>
-      <c r="I49" s="51"/>
-      <c r="J49" s="52"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="53"/>
+      <c r="D49" s="53"/>
+      <c r="E49" s="53"/>
+      <c r="F49" s="54"/>
+      <c r="G49" s="53"/>
+      <c r="H49" s="53"/>
+      <c r="I49" s="53"/>
+      <c r="J49" s="54"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="B50" s="50"/>
-      <c r="C50" s="51"/>
-      <c r="D50" s="51"/>
-      <c r="E50" s="51"/>
-      <c r="F50" s="52"/>
-      <c r="G50" s="51"/>
-      <c r="H50" s="51"/>
-      <c r="I50" s="51"/>
-      <c r="J50" s="52"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="53"/>
+      <c r="D50" s="53"/>
+      <c r="E50" s="53"/>
+      <c r="F50" s="54"/>
+      <c r="G50" s="53"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="53"/>
+      <c r="J50" s="54"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="B51" s="50"/>
-      <c r="C51" s="51"/>
-      <c r="D51" s="51"/>
-      <c r="E51" s="51"/>
-      <c r="F51" s="52"/>
-      <c r="G51" s="51"/>
-      <c r="H51" s="51"/>
-      <c r="I51" s="51"/>
-      <c r="J51" s="52"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="53"/>
+      <c r="D51" s="53"/>
+      <c r="E51" s="53"/>
+      <c r="F51" s="54"/>
+      <c r="G51" s="53"/>
+      <c r="H51" s="53"/>
+      <c r="I51" s="53"/>
+      <c r="J51" s="54"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="B52" s="50"/>
-      <c r="C52" s="51"/>
-      <c r="D52" s="51"/>
-      <c r="E52" s="51"/>
-      <c r="F52" s="52"/>
-      <c r="G52" s="51"/>
-      <c r="H52" s="51"/>
-      <c r="I52" s="51"/>
-      <c r="J52" s="52"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="53"/>
+      <c r="D52" s="53"/>
+      <c r="E52" s="53"/>
+      <c r="F52" s="54"/>
+      <c r="G52" s="53"/>
+      <c r="H52" s="53"/>
+      <c r="I52" s="53"/>
+      <c r="J52" s="54"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="B53" s="50"/>
-      <c r="C53" s="51"/>
-      <c r="D53" s="51"/>
-      <c r="E53" s="51"/>
-      <c r="F53" s="52"/>
-      <c r="G53" s="51"/>
-      <c r="H53" s="51"/>
-      <c r="I53" s="51"/>
-      <c r="J53" s="52"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="53"/>
+      <c r="D53" s="53"/>
+      <c r="E53" s="53"/>
+      <c r="F53" s="54"/>
+      <c r="G53" s="53"/>
+      <c r="H53" s="53"/>
+      <c r="I53" s="53"/>
+      <c r="J53" s="54"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="B54" s="50"/>
-      <c r="C54" s="51"/>
-      <c r="D54" s="51"/>
-      <c r="E54" s="51"/>
-      <c r="F54" s="52"/>
-      <c r="G54" s="51"/>
-      <c r="H54" s="51"/>
-      <c r="I54" s="51"/>
-      <c r="J54" s="52"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="53"/>
+      <c r="D54" s="53"/>
+      <c r="E54" s="53"/>
+      <c r="F54" s="54"/>
+      <c r="G54" s="53"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="53"/>
+      <c r="J54" s="54"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="B55" s="50"/>
-      <c r="C55" s="51"/>
-      <c r="D55" s="51"/>
-      <c r="E55" s="51"/>
-      <c r="F55" s="52"/>
-      <c r="G55" s="51"/>
-      <c r="H55" s="51"/>
-      <c r="I55" s="51"/>
-      <c r="J55" s="52"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="53"/>
+      <c r="D55" s="53"/>
+      <c r="E55" s="53"/>
+      <c r="F55" s="54"/>
+      <c r="G55" s="53"/>
+      <c r="H55" s="53"/>
+      <c r="I55" s="53"/>
+      <c r="J55" s="54"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="B56" s="50"/>
-      <c r="C56" s="51"/>
-      <c r="D56" s="51"/>
-      <c r="E56" s="51"/>
-      <c r="F56" s="52"/>
-      <c r="G56" s="51"/>
-      <c r="H56" s="51"/>
-      <c r="I56" s="51"/>
-      <c r="J56" s="52"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="53"/>
+      <c r="D56" s="53"/>
+      <c r="E56" s="53"/>
+      <c r="F56" s="54"/>
+      <c r="G56" s="53"/>
+      <c r="H56" s="53"/>
+      <c r="I56" s="53"/>
+      <c r="J56" s="54"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="B57" s="50"/>
-      <c r="C57" s="51"/>
-      <c r="D57" s="51"/>
-      <c r="E57" s="51"/>
-      <c r="F57" s="52"/>
-      <c r="G57" s="51"/>
-      <c r="H57" s="51"/>
-      <c r="I57" s="51"/>
-      <c r="J57" s="52"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="53"/>
+      <c r="D57" s="53"/>
+      <c r="E57" s="53"/>
+      <c r="F57" s="54"/>
+      <c r="G57" s="53"/>
+      <c r="H57" s="53"/>
+      <c r="I57" s="53"/>
+      <c r="J57" s="54"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="B58" s="50"/>
-      <c r="C58" s="51"/>
-      <c r="D58" s="51"/>
-      <c r="E58" s="51"/>
-      <c r="F58" s="52"/>
-      <c r="G58" s="51"/>
-      <c r="H58" s="51"/>
-      <c r="I58" s="51"/>
-      <c r="J58" s="52"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="53"/>
+      <c r="D58" s="53"/>
+      <c r="E58" s="53"/>
+      <c r="F58" s="54"/>
+      <c r="G58" s="53"/>
+      <c r="H58" s="53"/>
+      <c r="I58" s="53"/>
+      <c r="J58" s="54"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="B59" s="50"/>
-      <c r="C59" s="51"/>
-      <c r="D59" s="51"/>
-      <c r="E59" s="51"/>
-      <c r="F59" s="52"/>
-      <c r="G59" s="51"/>
-      <c r="H59" s="51"/>
-      <c r="I59" s="51"/>
-      <c r="J59" s="52"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="53"/>
+      <c r="D59" s="53"/>
+      <c r="E59" s="53"/>
+      <c r="F59" s="54"/>
+      <c r="G59" s="53"/>
+      <c r="H59" s="53"/>
+      <c r="I59" s="53"/>
+      <c r="J59" s="54"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="B60" s="50"/>
-      <c r="C60" s="51"/>
-      <c r="D60" s="51"/>
-      <c r="E60" s="51"/>
-      <c r="F60" s="52"/>
-      <c r="G60" s="51"/>
-      <c r="H60" s="51"/>
-      <c r="I60" s="51"/>
-      <c r="J60" s="52"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="53"/>
+      <c r="D60" s="53"/>
+      <c r="E60" s="53"/>
+      <c r="F60" s="54"/>
+      <c r="G60" s="53"/>
+      <c r="H60" s="53"/>
+      <c r="I60" s="53"/>
+      <c r="J60" s="54"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="B61" s="50"/>
-      <c r="C61" s="51"/>
-      <c r="D61" s="51"/>
-      <c r="E61" s="51"/>
-      <c r="F61" s="52"/>
-      <c r="G61" s="51"/>
-      <c r="H61" s="51"/>
-      <c r="I61" s="51"/>
-      <c r="J61" s="52"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="53"/>
+      <c r="D61" s="53"/>
+      <c r="E61" s="53"/>
+      <c r="F61" s="54"/>
+      <c r="G61" s="53"/>
+      <c r="H61" s="53"/>
+      <c r="I61" s="53"/>
+      <c r="J61" s="54"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="B62" s="50"/>
-      <c r="C62" s="51"/>
-      <c r="D62" s="51"/>
-      <c r="E62" s="51"/>
-      <c r="F62" s="52"/>
-      <c r="G62" s="51"/>
-      <c r="H62" s="51"/>
-      <c r="I62" s="51"/>
-      <c r="J62" s="52"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="53"/>
+      <c r="D62" s="53"/>
+      <c r="E62" s="53"/>
+      <c r="F62" s="54"/>
+      <c r="G62" s="53"/>
+      <c r="H62" s="53"/>
+      <c r="I62" s="53"/>
+      <c r="J62" s="54"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="B63" s="50"/>
-      <c r="C63" s="51"/>
-      <c r="D63" s="51"/>
-      <c r="E63" s="51"/>
-      <c r="F63" s="52"/>
-      <c r="G63" s="51"/>
-      <c r="H63" s="51"/>
-      <c r="I63" s="51"/>
-      <c r="J63" s="52"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="53"/>
+      <c r="D63" s="53"/>
+      <c r="E63" s="53"/>
+      <c r="F63" s="54"/>
+      <c r="G63" s="53"/>
+      <c r="H63" s="53"/>
+      <c r="I63" s="53"/>
+      <c r="J63" s="54"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="B64" s="50"/>
-      <c r="C64" s="51"/>
-      <c r="D64" s="51"/>
-      <c r="E64" s="51"/>
-      <c r="F64" s="52"/>
-      <c r="G64" s="51"/>
-      <c r="H64" s="51"/>
-      <c r="I64" s="51"/>
-      <c r="J64" s="52"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="53"/>
+      <c r="D64" s="53"/>
+      <c r="E64" s="53"/>
+      <c r="F64" s="54"/>
+      <c r="G64" s="53"/>
+      <c r="H64" s="53"/>
+      <c r="I64" s="53"/>
+      <c r="J64" s="54"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="B65" s="50"/>
-      <c r="C65" s="51"/>
-      <c r="D65" s="51"/>
-      <c r="E65" s="51"/>
-      <c r="F65" s="52"/>
-      <c r="G65" s="51"/>
-      <c r="H65" s="51"/>
-      <c r="I65" s="51"/>
-      <c r="J65" s="52"/>
+      <c r="B65" s="52"/>
+      <c r="C65" s="53"/>
+      <c r="D65" s="53"/>
+      <c r="E65" s="53"/>
+      <c r="F65" s="54"/>
+      <c r="G65" s="53"/>
+      <c r="H65" s="53"/>
+      <c r="I65" s="53"/>
+      <c r="J65" s="54"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="B66" s="50"/>
-      <c r="C66" s="51"/>
-      <c r="D66" s="51"/>
-      <c r="E66" s="51"/>
-      <c r="F66" s="52"/>
-      <c r="G66" s="51"/>
-      <c r="H66" s="51"/>
-      <c r="I66" s="51"/>
-      <c r="J66" s="52"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="53"/>
+      <c r="D66" s="53"/>
+      <c r="E66" s="53"/>
+      <c r="F66" s="54"/>
+      <c r="G66" s="53"/>
+      <c r="H66" s="53"/>
+      <c r="I66" s="53"/>
+      <c r="J66" s="54"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="B67" s="50"/>
-      <c r="C67" s="51"/>
-      <c r="D67" s="51"/>
-      <c r="E67" s="51"/>
-      <c r="F67" s="52"/>
-      <c r="G67" s="51"/>
-      <c r="H67" s="51"/>
-      <c r="I67" s="51"/>
-      <c r="J67" s="52"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="53"/>
+      <c r="D67" s="53"/>
+      <c r="E67" s="53"/>
+      <c r="F67" s="54"/>
+      <c r="G67" s="53"/>
+      <c r="H67" s="53"/>
+      <c r="I67" s="53"/>
+      <c r="J67" s="54"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="B68" s="50"/>
-      <c r="C68" s="51"/>
-      <c r="D68" s="51"/>
-      <c r="E68" s="51"/>
-      <c r="F68" s="52"/>
-      <c r="G68" s="51"/>
-      <c r="H68" s="51"/>
-      <c r="I68" s="51"/>
-      <c r="J68" s="52"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="53"/>
+      <c r="D68" s="53"/>
+      <c r="E68" s="53"/>
+      <c r="F68" s="54"/>
+      <c r="G68" s="53"/>
+      <c r="H68" s="53"/>
+      <c r="I68" s="53"/>
+      <c r="J68" s="54"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="B69" s="50"/>
-      <c r="C69" s="51"/>
-      <c r="D69" s="51"/>
-      <c r="E69" s="51"/>
-      <c r="F69" s="52"/>
-      <c r="G69" s="51"/>
-      <c r="H69" s="51"/>
-      <c r="I69" s="51"/>
-      <c r="J69" s="52"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="53"/>
+      <c r="D69" s="53"/>
+      <c r="E69" s="53"/>
+      <c r="F69" s="54"/>
+      <c r="G69" s="53"/>
+      <c r="H69" s="53"/>
+      <c r="I69" s="53"/>
+      <c r="J69" s="54"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="B70" s="50"/>
-      <c r="C70" s="51"/>
-      <c r="D70" s="51"/>
-      <c r="E70" s="51"/>
-      <c r="F70" s="52"/>
-      <c r="G70" s="51"/>
-      <c r="H70" s="51"/>
-      <c r="I70" s="51"/>
-      <c r="J70" s="52"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="53"/>
+      <c r="D70" s="53"/>
+      <c r="E70" s="53"/>
+      <c r="F70" s="54"/>
+      <c r="G70" s="53"/>
+      <c r="H70" s="53"/>
+      <c r="I70" s="53"/>
+      <c r="J70" s="54"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="B71" s="50"/>
-      <c r="C71" s="51"/>
-      <c r="D71" s="51"/>
-      <c r="E71" s="51"/>
-      <c r="F71" s="52"/>
-      <c r="G71" s="51"/>
-      <c r="H71" s="51"/>
-      <c r="I71" s="51"/>
-      <c r="J71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="53"/>
+      <c r="D71" s="53"/>
+      <c r="E71" s="53"/>
+      <c r="F71" s="54"/>
+      <c r="G71" s="53"/>
+      <c r="H71" s="53"/>
+      <c r="I71" s="53"/>
+      <c r="J71" s="54"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="B72" s="50"/>
-      <c r="C72" s="51"/>
-      <c r="D72" s="51"/>
-      <c r="E72" s="51"/>
-      <c r="F72" s="52"/>
-      <c r="G72" s="51"/>
-      <c r="H72" s="51"/>
-      <c r="I72" s="51"/>
-      <c r="J72" s="52"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="53"/>
+      <c r="D72" s="53"/>
+      <c r="E72" s="53"/>
+      <c r="F72" s="54"/>
+      <c r="G72" s="53"/>
+      <c r="H72" s="53"/>
+      <c r="I72" s="53"/>
+      <c r="J72" s="54"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="B73" s="50"/>
-      <c r="C73" s="51"/>
-      <c r="D73" s="51"/>
-      <c r="E73" s="51"/>
-      <c r="F73" s="52"/>
-      <c r="G73" s="51"/>
-      <c r="H73" s="51"/>
-      <c r="I73" s="51"/>
-      <c r="J73" s="52"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="53"/>
+      <c r="D73" s="53"/>
+      <c r="E73" s="53"/>
+      <c r="F73" s="54"/>
+      <c r="G73" s="53"/>
+      <c r="H73" s="53"/>
+      <c r="I73" s="53"/>
+      <c r="J73" s="54"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="B74" s="50"/>
-      <c r="C74" s="51"/>
-      <c r="D74" s="51"/>
-      <c r="E74" s="51"/>
-      <c r="F74" s="52"/>
-      <c r="G74" s="51"/>
-      <c r="H74" s="51"/>
-      <c r="I74" s="51"/>
-      <c r="J74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="53"/>
+      <c r="D74" s="53"/>
+      <c r="E74" s="53"/>
+      <c r="F74" s="54"/>
+      <c r="G74" s="53"/>
+      <c r="H74" s="53"/>
+      <c r="I74" s="53"/>
+      <c r="J74" s="54"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="B75" s="50"/>
-      <c r="C75" s="51"/>
-      <c r="D75" s="51"/>
-      <c r="E75" s="51"/>
-      <c r="F75" s="52"/>
-      <c r="G75" s="51"/>
-      <c r="H75" s="51"/>
-      <c r="I75" s="51"/>
-      <c r="J75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="53"/>
+      <c r="D75" s="53"/>
+      <c r="E75" s="53"/>
+      <c r="F75" s="54"/>
+      <c r="G75" s="53"/>
+      <c r="H75" s="53"/>
+      <c r="I75" s="53"/>
+      <c r="J75" s="54"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="B76" s="50"/>
-      <c r="C76" s="51"/>
-      <c r="D76" s="51"/>
-      <c r="E76" s="51"/>
-      <c r="F76" s="52"/>
-      <c r="G76" s="51"/>
-      <c r="H76" s="51"/>
-      <c r="I76" s="51"/>
-      <c r="J76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="53"/>
+      <c r="D76" s="53"/>
+      <c r="E76" s="53"/>
+      <c r="F76" s="54"/>
+      <c r="G76" s="53"/>
+      <c r="H76" s="53"/>
+      <c r="I76" s="53"/>
+      <c r="J76" s="54"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="B77" s="50"/>
-      <c r="C77" s="51"/>
-      <c r="D77" s="51"/>
-      <c r="E77" s="51"/>
-      <c r="F77" s="52"/>
-      <c r="G77" s="51"/>
-      <c r="H77" s="51"/>
-      <c r="I77" s="51"/>
-      <c r="J77" s="52"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="53"/>
+      <c r="D77" s="53"/>
+      <c r="E77" s="53"/>
+      <c r="F77" s="54"/>
+      <c r="G77" s="53"/>
+      <c r="H77" s="53"/>
+      <c r="I77" s="53"/>
+      <c r="J77" s="54"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="B78" s="50"/>
-      <c r="C78" s="51"/>
-      <c r="D78" s="51"/>
-      <c r="E78" s="51"/>
-      <c r="F78" s="52"/>
-      <c r="G78" s="51"/>
-      <c r="H78" s="51"/>
-      <c r="I78" s="51"/>
-      <c r="J78" s="52"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="53"/>
+      <c r="D78" s="53"/>
+      <c r="E78" s="53"/>
+      <c r="F78" s="54"/>
+      <c r="G78" s="53"/>
+      <c r="H78" s="53"/>
+      <c r="I78" s="53"/>
+      <c r="J78" s="54"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="B79" s="50"/>
-      <c r="C79" s="51"/>
-      <c r="D79" s="51"/>
-      <c r="E79" s="51"/>
-      <c r="F79" s="52"/>
-      <c r="G79" s="51"/>
-      <c r="H79" s="51"/>
-      <c r="I79" s="51"/>
-      <c r="J79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="53"/>
+      <c r="D79" s="53"/>
+      <c r="E79" s="53"/>
+      <c r="F79" s="54"/>
+      <c r="G79" s="53"/>
+      <c r="H79" s="53"/>
+      <c r="I79" s="53"/>
+      <c r="J79" s="54"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="B80" s="50"/>
-      <c r="C80" s="51"/>
-      <c r="D80" s="51"/>
-      <c r="E80" s="51"/>
-      <c r="F80" s="52"/>
-      <c r="G80" s="51"/>
-      <c r="H80" s="51"/>
-      <c r="I80" s="51"/>
-      <c r="J80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="53"/>
+      <c r="D80" s="53"/>
+      <c r="E80" s="53"/>
+      <c r="F80" s="54"/>
+      <c r="G80" s="53"/>
+      <c r="H80" s="53"/>
+      <c r="I80" s="53"/>
+      <c r="J80" s="54"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="B81" s="50"/>
-      <c r="C81" s="51"/>
-      <c r="D81" s="51"/>
-      <c r="E81" s="51"/>
-      <c r="F81" s="52"/>
-      <c r="G81" s="51"/>
-      <c r="H81" s="51"/>
-      <c r="I81" s="51"/>
-      <c r="J81" s="52"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="53"/>
+      <c r="D81" s="53"/>
+      <c r="E81" s="53"/>
+      <c r="F81" s="54"/>
+      <c r="G81" s="53"/>
+      <c r="H81" s="53"/>
+      <c r="I81" s="53"/>
+      <c r="J81" s="54"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="B82" s="50"/>
-      <c r="C82" s="51"/>
-      <c r="D82" s="51"/>
-      <c r="E82" s="51"/>
-      <c r="F82" s="52"/>
-      <c r="G82" s="51"/>
-      <c r="H82" s="51"/>
-      <c r="I82" s="51"/>
-      <c r="J82" s="52"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="53"/>
+      <c r="D82" s="53"/>
+      <c r="E82" s="53"/>
+      <c r="F82" s="54"/>
+      <c r="G82" s="53"/>
+      <c r="H82" s="53"/>
+      <c r="I82" s="53"/>
+      <c r="J82" s="54"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="B83" s="50"/>
-      <c r="C83" s="51"/>
-      <c r="D83" s="51"/>
-      <c r="E83" s="51"/>
-      <c r="F83" s="52"/>
-      <c r="G83" s="51"/>
-      <c r="H83" s="51"/>
-      <c r="I83" s="51"/>
-      <c r="J83" s="52"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="53"/>
+      <c r="D83" s="53"/>
+      <c r="E83" s="53"/>
+      <c r="F83" s="54"/>
+      <c r="G83" s="53"/>
+      <c r="H83" s="53"/>
+      <c r="I83" s="53"/>
+      <c r="J83" s="54"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="B84" s="50"/>
-      <c r="C84" s="51"/>
-      <c r="D84" s="51"/>
-      <c r="E84" s="51"/>
-      <c r="F84" s="52"/>
-      <c r="G84" s="51"/>
-      <c r="H84" s="51"/>
-      <c r="I84" s="51"/>
-      <c r="J84" s="52"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="53"/>
+      <c r="D84" s="53"/>
+      <c r="E84" s="53"/>
+      <c r="F84" s="54"/>
+      <c r="G84" s="53"/>
+      <c r="H84" s="53"/>
+      <c r="I84" s="53"/>
+      <c r="J84" s="54"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="B85" s="50"/>
-      <c r="C85" s="51"/>
-      <c r="D85" s="51"/>
-      <c r="E85" s="51"/>
-      <c r="F85" s="52"/>
-      <c r="G85" s="51"/>
-      <c r="H85" s="51"/>
-      <c r="I85" s="51"/>
-      <c r="J85" s="52"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="53"/>
+      <c r="D85" s="53"/>
+      <c r="E85" s="53"/>
+      <c r="F85" s="54"/>
+      <c r="G85" s="53"/>
+      <c r="H85" s="53"/>
+      <c r="I85" s="53"/>
+      <c r="J85" s="54"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="B86" s="50"/>
-      <c r="C86" s="51"/>
-      <c r="D86" s="51"/>
-      <c r="E86" s="51"/>
-      <c r="F86" s="52"/>
-      <c r="G86" s="51"/>
-      <c r="H86" s="51"/>
-      <c r="I86" s="51"/>
-      <c r="J86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="53"/>
+      <c r="D86" s="53"/>
+      <c r="E86" s="53"/>
+      <c r="F86" s="54"/>
+      <c r="G86" s="53"/>
+      <c r="H86" s="53"/>
+      <c r="I86" s="53"/>
+      <c r="J86" s="54"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="B87" s="50"/>
-      <c r="C87" s="51"/>
-      <c r="D87" s="51"/>
-      <c r="E87" s="51"/>
-      <c r="F87" s="52"/>
-      <c r="G87" s="51"/>
-      <c r="H87" s="51"/>
-      <c r="I87" s="51"/>
-      <c r="J87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="53"/>
+      <c r="D87" s="53"/>
+      <c r="E87" s="53"/>
+      <c r="F87" s="54"/>
+      <c r="G87" s="53"/>
+      <c r="H87" s="53"/>
+      <c r="I87" s="53"/>
+      <c r="J87" s="54"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="B88" s="50"/>
-      <c r="C88" s="51"/>
-      <c r="D88" s="51"/>
-      <c r="E88" s="51"/>
-      <c r="F88" s="52"/>
-      <c r="G88" s="51"/>
-      <c r="H88" s="51"/>
-      <c r="I88" s="51"/>
-      <c r="J88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="53"/>
+      <c r="D88" s="53"/>
+      <c r="E88" s="53"/>
+      <c r="F88" s="54"/>
+      <c r="G88" s="53"/>
+      <c r="H88" s="53"/>
+      <c r="I88" s="53"/>
+      <c r="J88" s="54"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="B89" s="50"/>
-      <c r="C89" s="51"/>
-      <c r="D89" s="51"/>
-      <c r="E89" s="51"/>
-      <c r="F89" s="52"/>
-      <c r="G89" s="51"/>
-      <c r="H89" s="51"/>
-      <c r="I89" s="51"/>
-      <c r="J89" s="52"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="53"/>
+      <c r="D89" s="53"/>
+      <c r="E89" s="53"/>
+      <c r="F89" s="54"/>
+      <c r="G89" s="53"/>
+      <c r="H89" s="53"/>
+      <c r="I89" s="53"/>
+      <c r="J89" s="54"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="B90" s="50"/>
-      <c r="C90" s="51"/>
-      <c r="D90" s="51"/>
-      <c r="E90" s="51"/>
-      <c r="F90" s="52"/>
-      <c r="G90" s="51"/>
-      <c r="H90" s="51"/>
-      <c r="I90" s="51"/>
-      <c r="J90" s="52"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="53"/>
+      <c r="D90" s="53"/>
+      <c r="E90" s="53"/>
+      <c r="F90" s="54"/>
+      <c r="G90" s="53"/>
+      <c r="H90" s="53"/>
+      <c r="I90" s="53"/>
+      <c r="J90" s="54"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="B91" s="50"/>
-      <c r="C91" s="51"/>
-      <c r="D91" s="51"/>
-      <c r="E91" s="51"/>
-      <c r="F91" s="52"/>
-      <c r="G91" s="51"/>
-      <c r="H91" s="51"/>
-      <c r="I91" s="51"/>
-      <c r="J91" s="52"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="53"/>
+      <c r="D91" s="53"/>
+      <c r="E91" s="53"/>
+      <c r="F91" s="54"/>
+      <c r="G91" s="53"/>
+      <c r="H91" s="53"/>
+      <c r="I91" s="53"/>
+      <c r="J91" s="54"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="B92" s="50"/>
-      <c r="C92" s="51"/>
-      <c r="D92" s="51"/>
-      <c r="E92" s="51"/>
-      <c r="F92" s="52"/>
-      <c r="G92" s="51"/>
-      <c r="H92" s="51"/>
-      <c r="I92" s="51"/>
-      <c r="J92" s="52"/>
+      <c r="B92" s="52"/>
+      <c r="C92" s="53"/>
+      <c r="D92" s="53"/>
+      <c r="E92" s="53"/>
+      <c r="F92" s="54"/>
+      <c r="G92" s="53"/>
+      <c r="H92" s="53"/>
+      <c r="I92" s="53"/>
+      <c r="J92" s="54"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="B93" s="50"/>
-      <c r="C93" s="51"/>
-      <c r="D93" s="51"/>
-      <c r="E93" s="51"/>
-      <c r="F93" s="52"/>
-      <c r="G93" s="51"/>
-      <c r="H93" s="51"/>
-      <c r="I93" s="51"/>
-      <c r="J93" s="52"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="53"/>
+      <c r="D93" s="53"/>
+      <c r="E93" s="53"/>
+      <c r="F93" s="54"/>
+      <c r="G93" s="53"/>
+      <c r="H93" s="53"/>
+      <c r="I93" s="53"/>
+      <c r="J93" s="54"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="B94" s="50"/>
-      <c r="C94" s="51"/>
-      <c r="D94" s="51"/>
-      <c r="E94" s="51"/>
-      <c r="F94" s="52"/>
-      <c r="G94" s="51"/>
-      <c r="H94" s="51"/>
-      <c r="I94" s="51"/>
-      <c r="J94" s="52"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="53"/>
+      <c r="D94" s="53"/>
+      <c r="E94" s="53"/>
+      <c r="F94" s="54"/>
+      <c r="G94" s="53"/>
+      <c r="H94" s="53"/>
+      <c r="I94" s="53"/>
+      <c r="J94" s="54"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="B95" s="50"/>
-      <c r="C95" s="51"/>
-      <c r="D95" s="51"/>
-      <c r="E95" s="51"/>
-      <c r="F95" s="52"/>
-      <c r="G95" s="51"/>
-      <c r="H95" s="51"/>
-      <c r="I95" s="51"/>
-      <c r="J95" s="52"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="53"/>
+      <c r="D95" s="53"/>
+      <c r="E95" s="53"/>
+      <c r="F95" s="54"/>
+      <c r="G95" s="53"/>
+      <c r="H95" s="53"/>
+      <c r="I95" s="53"/>
+      <c r="J95" s="54"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="B96" s="50"/>
-      <c r="C96" s="51"/>
-      <c r="D96" s="51"/>
-      <c r="E96" s="51"/>
-      <c r="F96" s="52"/>
-      <c r="G96" s="51"/>
-      <c r="H96" s="51"/>
-      <c r="I96" s="51"/>
-      <c r="J96" s="52"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="53"/>
+      <c r="D96" s="53"/>
+      <c r="E96" s="53"/>
+      <c r="F96" s="54"/>
+      <c r="G96" s="53"/>
+      <c r="H96" s="53"/>
+      <c r="I96" s="53"/>
+      <c r="J96" s="54"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="B97" s="50"/>
-      <c r="C97" s="51"/>
-      <c r="D97" s="51"/>
-      <c r="E97" s="51"/>
-      <c r="F97" s="52"/>
-      <c r="G97" s="51"/>
-      <c r="H97" s="51"/>
-      <c r="I97" s="51"/>
-      <c r="J97" s="52"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="53"/>
+      <c r="D97" s="53"/>
+      <c r="E97" s="53"/>
+      <c r="F97" s="54"/>
+      <c r="G97" s="53"/>
+      <c r="H97" s="53"/>
+      <c r="I97" s="53"/>
+      <c r="J97" s="54"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="B98" s="50"/>
-      <c r="C98" s="51"/>
-      <c r="D98" s="51"/>
-      <c r="E98" s="51"/>
-      <c r="F98" s="52"/>
-      <c r="G98" s="51"/>
-      <c r="H98" s="51"/>
-      <c r="I98" s="51"/>
-      <c r="J98" s="52"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="53"/>
+      <c r="D98" s="53"/>
+      <c r="E98" s="53"/>
+      <c r="F98" s="54"/>
+      <c r="G98" s="53"/>
+      <c r="H98" s="53"/>
+      <c r="I98" s="53"/>
+      <c r="J98" s="54"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="B99" s="50"/>
-      <c r="C99" s="51"/>
-      <c r="D99" s="51"/>
-      <c r="E99" s="51"/>
-      <c r="F99" s="52"/>
-      <c r="G99" s="51"/>
-      <c r="H99" s="51"/>
-      <c r="I99" s="51"/>
-      <c r="J99" s="52"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="53"/>
+      <c r="D99" s="53"/>
+      <c r="E99" s="53"/>
+      <c r="F99" s="54"/>
+      <c r="G99" s="53"/>
+      <c r="H99" s="53"/>
+      <c r="I99" s="53"/>
+      <c r="J99" s="54"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="B100" s="50"/>
-      <c r="C100" s="51"/>
-      <c r="D100" s="51"/>
-      <c r="E100" s="51"/>
-      <c r="F100" s="52"/>
-      <c r="G100" s="51"/>
-      <c r="H100" s="51"/>
-      <c r="I100" s="51"/>
-      <c r="J100" s="52"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="53"/>
+      <c r="D100" s="53"/>
+      <c r="E100" s="53"/>
+      <c r="F100" s="54"/>
+      <c r="G100" s="53"/>
+      <c r="H100" s="53"/>
+      <c r="I100" s="53"/>
+      <c r="J100" s="54"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="B101" s="50"/>
-      <c r="C101" s="51"/>
-      <c r="D101" s="51"/>
-      <c r="E101" s="51"/>
-      <c r="F101" s="52"/>
-      <c r="G101" s="51"/>
-      <c r="H101" s="51"/>
-      <c r="I101" s="51"/>
-      <c r="J101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="53"/>
+      <c r="D101" s="53"/>
+      <c r="E101" s="53"/>
+      <c r="F101" s="54"/>
+      <c r="G101" s="53"/>
+      <c r="H101" s="53"/>
+      <c r="I101" s="53"/>
+      <c r="J101" s="54"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="B102" s="50"/>
-      <c r="C102" s="51"/>
-      <c r="D102" s="51"/>
-      <c r="E102" s="51"/>
-      <c r="F102" s="52"/>
-      <c r="G102" s="51"/>
-      <c r="H102" s="51"/>
-      <c r="I102" s="51"/>
-      <c r="J102" s="52"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="53"/>
+      <c r="D102" s="53"/>
+      <c r="E102" s="53"/>
+      <c r="F102" s="54"/>
+      <c r="G102" s="53"/>
+      <c r="H102" s="53"/>
+      <c r="I102" s="53"/>
+      <c r="J102" s="54"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="B103" s="50"/>
-      <c r="C103" s="51"/>
-      <c r="D103" s="51"/>
-      <c r="E103" s="51"/>
-      <c r="F103" s="52"/>
-      <c r="G103" s="51"/>
-      <c r="H103" s="51"/>
-      <c r="I103" s="51"/>
-      <c r="J103" s="52"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="53"/>
+      <c r="D103" s="53"/>
+      <c r="E103" s="53"/>
+      <c r="F103" s="54"/>
+      <c r="G103" s="53"/>
+      <c r="H103" s="53"/>
+      <c r="I103" s="53"/>
+      <c r="J103" s="54"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="B104" s="50"/>
-      <c r="C104" s="51"/>
-      <c r="D104" s="51"/>
-      <c r="E104" s="51"/>
-      <c r="F104" s="52"/>
-      <c r="G104" s="51"/>
-      <c r="H104" s="51"/>
-      <c r="I104" s="51"/>
-      <c r="J104" s="52"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="53"/>
+      <c r="D104" s="53"/>
+      <c r="E104" s="53"/>
+      <c r="F104" s="54"/>
+      <c r="G104" s="53"/>
+      <c r="H104" s="53"/>
+      <c r="I104" s="53"/>
+      <c r="J104" s="54"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="B105" s="50"/>
-      <c r="C105" s="51"/>
-      <c r="D105" s="51"/>
-      <c r="E105" s="51"/>
-      <c r="F105" s="52"/>
-      <c r="G105" s="51"/>
-      <c r="H105" s="51"/>
-      <c r="I105" s="51"/>
-      <c r="J105" s="52"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="53"/>
+      <c r="D105" s="53"/>
+      <c r="E105" s="53"/>
+      <c r="F105" s="54"/>
+      <c r="G105" s="53"/>
+      <c r="H105" s="53"/>
+      <c r="I105" s="53"/>
+      <c r="J105" s="54"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="B106" s="50"/>
-      <c r="C106" s="51"/>
-      <c r="D106" s="51"/>
-      <c r="E106" s="51"/>
-      <c r="F106" s="52"/>
-      <c r="G106" s="51"/>
-      <c r="H106" s="51"/>
-      <c r="I106" s="51"/>
-      <c r="J106" s="52"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="53"/>
+      <c r="D106" s="53"/>
+      <c r="E106" s="53"/>
+      <c r="F106" s="54"/>
+      <c r="G106" s="53"/>
+      <c r="H106" s="53"/>
+      <c r="I106" s="53"/>
+      <c r="J106" s="54"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="B107" s="50"/>
-      <c r="C107" s="51"/>
-      <c r="D107" s="51"/>
-      <c r="E107" s="51"/>
-      <c r="F107" s="52"/>
-      <c r="G107" s="51"/>
-      <c r="H107" s="51"/>
-      <c r="I107" s="51"/>
-      <c r="J107" s="52"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="53"/>
+      <c r="D107" s="53"/>
+      <c r="E107" s="53"/>
+      <c r="F107" s="54"/>
+      <c r="G107" s="53"/>
+      <c r="H107" s="53"/>
+      <c r="I107" s="53"/>
+      <c r="J107" s="54"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="B108" s="50"/>
-      <c r="C108" s="51"/>
-      <c r="D108" s="51"/>
-      <c r="E108" s="51"/>
-      <c r="F108" s="52"/>
-      <c r="G108" s="51"/>
-      <c r="H108" s="51"/>
-      <c r="I108" s="51"/>
-      <c r="J108" s="52"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="53"/>
+      <c r="D108" s="53"/>
+      <c r="E108" s="53"/>
+      <c r="F108" s="54"/>
+      <c r="G108" s="53"/>
+      <c r="H108" s="53"/>
+      <c r="I108" s="53"/>
+      <c r="J108" s="54"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="B109" s="50"/>
-      <c r="C109" s="51"/>
-      <c r="D109" s="51"/>
-      <c r="E109" s="51"/>
-      <c r="F109" s="52"/>
-      <c r="G109" s="51"/>
-      <c r="H109" s="51"/>
-      <c r="I109" s="51"/>
-      <c r="J109" s="52"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="53"/>
+      <c r="D109" s="53"/>
+      <c r="E109" s="53"/>
+      <c r="F109" s="54"/>
+      <c r="G109" s="53"/>
+      <c r="H109" s="53"/>
+      <c r="I109" s="53"/>
+      <c r="J109" s="54"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="B110" s="50"/>
-      <c r="C110" s="51"/>
-      <c r="D110" s="51"/>
-      <c r="E110" s="51"/>
-      <c r="F110" s="52"/>
-      <c r="G110" s="51"/>
-      <c r="H110" s="51"/>
-      <c r="I110" s="51"/>
-      <c r="J110" s="52"/>
+      <c r="B110" s="52"/>
+      <c r="C110" s="53"/>
+      <c r="D110" s="53"/>
+      <c r="E110" s="53"/>
+      <c r="F110" s="54"/>
+      <c r="G110" s="53"/>
+      <c r="H110" s="53"/>
+      <c r="I110" s="53"/>
+      <c r="J110" s="54"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="B111" s="50"/>
-      <c r="C111" s="51"/>
-      <c r="D111" s="51"/>
-      <c r="E111" s="51"/>
-      <c r="F111" s="52"/>
-      <c r="G111" s="51"/>
-      <c r="H111" s="51"/>
-      <c r="I111" s="51"/>
-      <c r="J111" s="52"/>
+      <c r="B111" s="52"/>
+      <c r="C111" s="53"/>
+      <c r="D111" s="53"/>
+      <c r="E111" s="53"/>
+      <c r="F111" s="54"/>
+      <c r="G111" s="53"/>
+      <c r="H111" s="53"/>
+      <c r="I111" s="53"/>
+      <c r="J111" s="54"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="B112" s="50"/>
-      <c r="C112" s="51"/>
-      <c r="D112" s="51"/>
-      <c r="E112" s="51"/>
-      <c r="F112" s="52"/>
-      <c r="G112" s="51"/>
-      <c r="H112" s="51"/>
-      <c r="I112" s="51"/>
-      <c r="J112" s="52"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="53"/>
+      <c r="D112" s="53"/>
+      <c r="E112" s="53"/>
+      <c r="F112" s="54"/>
+      <c r="G112" s="53"/>
+      <c r="H112" s="53"/>
+      <c r="I112" s="53"/>
+      <c r="J112" s="54"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="B113" s="50"/>
-      <c r="C113" s="51"/>
-      <c r="D113" s="51"/>
-      <c r="E113" s="51"/>
-      <c r="F113" s="52"/>
-      <c r="G113" s="51"/>
-      <c r="H113" s="51"/>
-      <c r="I113" s="51"/>
-      <c r="J113" s="52"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="53"/>
+      <c r="D113" s="53"/>
+      <c r="E113" s="53"/>
+      <c r="F113" s="54"/>
+      <c r="G113" s="53"/>
+      <c r="H113" s="53"/>
+      <c r="I113" s="53"/>
+      <c r="J113" s="54"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="B114" s="50"/>
-      <c r="C114" s="51"/>
-      <c r="D114" s="51"/>
-      <c r="E114" s="51"/>
-      <c r="F114" s="52"/>
-      <c r="G114" s="51"/>
-      <c r="H114" s="51"/>
-      <c r="I114" s="51"/>
-      <c r="J114" s="52"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="53"/>
+      <c r="D114" s="53"/>
+      <c r="E114" s="53"/>
+      <c r="F114" s="54"/>
+      <c r="G114" s="53"/>
+      <c r="H114" s="53"/>
+      <c r="I114" s="53"/>
+      <c r="J114" s="54"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="B115" s="50"/>
-      <c r="C115" s="51"/>
-      <c r="D115" s="51"/>
-      <c r="E115" s="51"/>
-      <c r="F115" s="52"/>
-      <c r="G115" s="51"/>
-      <c r="H115" s="51"/>
-      <c r="I115" s="51"/>
-      <c r="J115" s="52"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="53"/>
+      <c r="D115" s="53"/>
+      <c r="E115" s="53"/>
+      <c r="F115" s="54"/>
+      <c r="G115" s="53"/>
+      <c r="H115" s="53"/>
+      <c r="I115" s="53"/>
+      <c r="J115" s="54"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="B116" s="50"/>
-      <c r="C116" s="51"/>
-      <c r="D116" s="51"/>
-      <c r="E116" s="51"/>
-      <c r="F116" s="52"/>
-      <c r="G116" s="51"/>
-      <c r="H116" s="51"/>
-      <c r="I116" s="51"/>
-      <c r="J116" s="52"/>
+      <c r="B116" s="52"/>
+      <c r="C116" s="53"/>
+      <c r="D116" s="53"/>
+      <c r="E116" s="53"/>
+      <c r="F116" s="54"/>
+      <c r="G116" s="53"/>
+      <c r="H116" s="53"/>
+      <c r="I116" s="53"/>
+      <c r="J116" s="54"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="B117" s="50"/>
-      <c r="C117" s="51"/>
-      <c r="D117" s="51"/>
-      <c r="E117" s="51"/>
-      <c r="F117" s="52"/>
-      <c r="G117" s="51"/>
-      <c r="H117" s="51"/>
-      <c r="I117" s="51"/>
-      <c r="J117" s="52"/>
+      <c r="B117" s="52"/>
+      <c r="C117" s="53"/>
+      <c r="D117" s="53"/>
+      <c r="E117" s="53"/>
+      <c r="F117" s="54"/>
+      <c r="G117" s="53"/>
+      <c r="H117" s="53"/>
+      <c r="I117" s="53"/>
+      <c r="J117" s="54"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="B118" s="50"/>
-      <c r="C118" s="51"/>
-      <c r="D118" s="51"/>
-      <c r="E118" s="51"/>
-      <c r="F118" s="52"/>
-      <c r="G118" s="51"/>
-      <c r="H118" s="51"/>
-      <c r="I118" s="51"/>
-      <c r="J118" s="52"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="53"/>
+      <c r="D118" s="53"/>
+      <c r="E118" s="53"/>
+      <c r="F118" s="54"/>
+      <c r="G118" s="53"/>
+      <c r="H118" s="53"/>
+      <c r="I118" s="53"/>
+      <c r="J118" s="54"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="B119" s="50"/>
-      <c r="C119" s="51"/>
-      <c r="D119" s="51"/>
-      <c r="E119" s="51"/>
-      <c r="F119" s="52"/>
-      <c r="G119" s="51"/>
-      <c r="H119" s="51"/>
-      <c r="I119" s="51"/>
-      <c r="J119" s="52"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="53"/>
+      <c r="D119" s="53"/>
+      <c r="E119" s="53"/>
+      <c r="F119" s="54"/>
+      <c r="G119" s="53"/>
+      <c r="H119" s="53"/>
+      <c r="I119" s="53"/>
+      <c r="J119" s="54"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="B120" s="50"/>
-      <c r="C120" s="51"/>
-      <c r="D120" s="51"/>
-      <c r="E120" s="51"/>
-      <c r="F120" s="52"/>
-      <c r="G120" s="51"/>
-      <c r="H120" s="51"/>
-      <c r="I120" s="51"/>
-      <c r="J120" s="52"/>
+      <c r="B120" s="52"/>
+      <c r="C120" s="53"/>
+      <c r="D120" s="53"/>
+      <c r="E120" s="53"/>
+      <c r="F120" s="54"/>
+      <c r="G120" s="53"/>
+      <c r="H120" s="53"/>
+      <c r="I120" s="53"/>
+      <c r="J120" s="54"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="B121" s="50"/>
-      <c r="C121" s="51"/>
-      <c r="D121" s="51"/>
-      <c r="E121" s="51"/>
-      <c r="F121" s="52"/>
-      <c r="G121" s="51"/>
-      <c r="H121" s="51"/>
-      <c r="I121" s="51"/>
-      <c r="J121" s="52"/>
+      <c r="B121" s="52"/>
+      <c r="C121" s="53"/>
+      <c r="D121" s="53"/>
+      <c r="E121" s="53"/>
+      <c r="F121" s="54"/>
+      <c r="G121" s="53"/>
+      <c r="H121" s="53"/>
+      <c r="I121" s="53"/>
+      <c r="J121" s="54"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="B122" s="50"/>
-      <c r="C122" s="51"/>
-      <c r="D122" s="51"/>
-      <c r="E122" s="51"/>
-      <c r="F122" s="52"/>
-      <c r="G122" s="51"/>
-      <c r="H122" s="51"/>
-      <c r="I122" s="51"/>
-      <c r="J122" s="52"/>
+      <c r="B122" s="52"/>
+      <c r="C122" s="53"/>
+      <c r="D122" s="53"/>
+      <c r="E122" s="53"/>
+      <c r="F122" s="54"/>
+      <c r="G122" s="53"/>
+      <c r="H122" s="53"/>
+      <c r="I122" s="53"/>
+      <c r="J122" s="54"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="B123" s="50"/>
-      <c r="C123" s="51"/>
-      <c r="D123" s="51"/>
-      <c r="E123" s="51"/>
-      <c r="F123" s="52"/>
-      <c r="G123" s="51"/>
-      <c r="H123" s="51"/>
-      <c r="I123" s="51"/>
-      <c r="J123" s="52"/>
+      <c r="B123" s="52"/>
+      <c r="C123" s="53"/>
+      <c r="D123" s="53"/>
+      <c r="E123" s="53"/>
+      <c r="F123" s="54"/>
+      <c r="G123" s="53"/>
+      <c r="H123" s="53"/>
+      <c r="I123" s="53"/>
+      <c r="J123" s="54"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="B124" s="50"/>
-      <c r="C124" s="51"/>
-      <c r="D124" s="51"/>
-      <c r="E124" s="51"/>
-      <c r="F124" s="52"/>
-      <c r="G124" s="51"/>
-      <c r="H124" s="51"/>
-      <c r="I124" s="51"/>
-      <c r="J124" s="52"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="53"/>
+      <c r="D124" s="53"/>
+      <c r="E124" s="53"/>
+      <c r="F124" s="54"/>
+      <c r="G124" s="53"/>
+      <c r="H124" s="53"/>
+      <c r="I124" s="53"/>
+      <c r="J124" s="54"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="B125" s="50"/>
-      <c r="C125" s="51"/>
-      <c r="D125" s="51"/>
-      <c r="E125" s="51"/>
-      <c r="F125" s="52"/>
-      <c r="G125" s="51"/>
-      <c r="H125" s="51"/>
-      <c r="I125" s="51"/>
-      <c r="J125" s="52"/>
+      <c r="B125" s="52"/>
+      <c r="C125" s="53"/>
+      <c r="D125" s="53"/>
+      <c r="E125" s="53"/>
+      <c r="F125" s="54"/>
+      <c r="G125" s="53"/>
+      <c r="H125" s="53"/>
+      <c r="I125" s="53"/>
+      <c r="J125" s="54"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="B126" s="50"/>
-      <c r="C126" s="51"/>
-      <c r="D126" s="51"/>
-      <c r="E126" s="51"/>
-      <c r="F126" s="52"/>
-      <c r="G126" s="51"/>
-      <c r="H126" s="51"/>
-      <c r="I126" s="51"/>
-      <c r="J126" s="52"/>
+      <c r="B126" s="52"/>
+      <c r="C126" s="53"/>
+      <c r="D126" s="53"/>
+      <c r="E126" s="53"/>
+      <c r="F126" s="54"/>
+      <c r="G126" s="53"/>
+      <c r="H126" s="53"/>
+      <c r="I126" s="53"/>
+      <c r="J126" s="54"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="B127" s="50"/>
-      <c r="C127" s="51"/>
-      <c r="D127" s="51"/>
-      <c r="E127" s="51"/>
-      <c r="F127" s="52"/>
-      <c r="G127" s="51"/>
-      <c r="H127" s="51"/>
-      <c r="I127" s="51"/>
-      <c r="J127" s="52"/>
+      <c r="B127" s="52"/>
+      <c r="C127" s="53"/>
+      <c r="D127" s="53"/>
+      <c r="E127" s="53"/>
+      <c r="F127" s="54"/>
+      <c r="G127" s="53"/>
+      <c r="H127" s="53"/>
+      <c r="I127" s="53"/>
+      <c r="J127" s="54"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="B128" s="50"/>
-      <c r="C128" s="51"/>
-      <c r="D128" s="51"/>
-      <c r="E128" s="51"/>
-      <c r="F128" s="52"/>
-      <c r="G128" s="51"/>
-      <c r="H128" s="51"/>
-      <c r="I128" s="51"/>
-      <c r="J128" s="52"/>
+      <c r="B128" s="52"/>
+      <c r="C128" s="53"/>
+      <c r="D128" s="53"/>
+      <c r="E128" s="53"/>
+      <c r="F128" s="54"/>
+      <c r="G128" s="53"/>
+      <c r="H128" s="53"/>
+      <c r="I128" s="53"/>
+      <c r="J128" s="54"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="B129" s="50"/>
-      <c r="C129" s="51"/>
-      <c r="D129" s="51"/>
-      <c r="E129" s="51"/>
-      <c r="F129" s="52"/>
-      <c r="G129" s="51"/>
-      <c r="H129" s="51"/>
-      <c r="I129" s="51"/>
-      <c r="J129" s="52"/>
+      <c r="B129" s="52"/>
+      <c r="C129" s="53"/>
+      <c r="D129" s="53"/>
+      <c r="E129" s="53"/>
+      <c r="F129" s="54"/>
+      <c r="G129" s="53"/>
+      <c r="H129" s="53"/>
+      <c r="I129" s="53"/>
+      <c r="J129" s="54"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="B130" s="50"/>
-      <c r="C130" s="51"/>
-      <c r="D130" s="51"/>
-      <c r="E130" s="51"/>
-      <c r="F130" s="52"/>
-      <c r="G130" s="51"/>
-      <c r="H130" s="51"/>
-      <c r="I130" s="51"/>
-      <c r="J130" s="52"/>
+      <c r="B130" s="52"/>
+      <c r="C130" s="53"/>
+      <c r="D130" s="53"/>
+      <c r="E130" s="53"/>
+      <c r="F130" s="54"/>
+      <c r="G130" s="53"/>
+      <c r="H130" s="53"/>
+      <c r="I130" s="53"/>
+      <c r="J130" s="54"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="B131" s="50"/>
-      <c r="C131" s="51"/>
-      <c r="D131" s="51"/>
-      <c r="E131" s="51"/>
-      <c r="F131" s="52"/>
-      <c r="G131" s="51"/>
-      <c r="H131" s="51"/>
-      <c r="I131" s="51"/>
-      <c r="J131" s="52"/>
+      <c r="B131" s="52"/>
+      <c r="C131" s="53"/>
+      <c r="D131" s="53"/>
+      <c r="E131" s="53"/>
+      <c r="F131" s="54"/>
+      <c r="G131" s="53"/>
+      <c r="H131" s="53"/>
+      <c r="I131" s="53"/>
+      <c r="J131" s="54"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="B132" s="50"/>
-      <c r="C132" s="51"/>
-      <c r="D132" s="51"/>
-      <c r="E132" s="51"/>
-      <c r="F132" s="52"/>
-      <c r="G132" s="51"/>
-      <c r="H132" s="51"/>
-      <c r="I132" s="51"/>
-      <c r="J132" s="52"/>
+      <c r="B132" s="52"/>
+      <c r="C132" s="53"/>
+      <c r="D132" s="53"/>
+      <c r="E132" s="53"/>
+      <c r="F132" s="54"/>
+      <c r="G132" s="53"/>
+      <c r="H132" s="53"/>
+      <c r="I132" s="53"/>
+      <c r="J132" s="54"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="B133" s="50"/>
-      <c r="C133" s="51"/>
-      <c r="D133" s="51"/>
-      <c r="E133" s="51"/>
-      <c r="F133" s="52"/>
-      <c r="G133" s="51"/>
-      <c r="H133" s="51"/>
-      <c r="I133" s="51"/>
-      <c r="J133" s="52"/>
+      <c r="B133" s="52"/>
+      <c r="C133" s="53"/>
+      <c r="D133" s="53"/>
+      <c r="E133" s="53"/>
+      <c r="F133" s="54"/>
+      <c r="G133" s="53"/>
+      <c r="H133" s="53"/>
+      <c r="I133" s="53"/>
+      <c r="J133" s="54"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="B134" s="50"/>
-      <c r="C134" s="51"/>
-      <c r="D134" s="51"/>
-      <c r="E134" s="51"/>
-      <c r="F134" s="52"/>
-      <c r="G134" s="51"/>
-      <c r="H134" s="51"/>
-      <c r="I134" s="51"/>
-      <c r="J134" s="52"/>
+      <c r="B134" s="52"/>
+      <c r="C134" s="53"/>
+      <c r="D134" s="53"/>
+      <c r="E134" s="53"/>
+      <c r="F134" s="54"/>
+      <c r="G134" s="53"/>
+      <c r="H134" s="53"/>
+      <c r="I134" s="53"/>
+      <c r="J134" s="54"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="B135" s="50"/>
-      <c r="C135" s="51"/>
-      <c r="D135" s="51"/>
-      <c r="E135" s="51"/>
-      <c r="F135" s="52"/>
-      <c r="G135" s="51"/>
-      <c r="H135" s="51"/>
-      <c r="I135" s="51"/>
-      <c r="J135" s="52"/>
+      <c r="B135" s="52"/>
+      <c r="C135" s="53"/>
+      <c r="D135" s="53"/>
+      <c r="E135" s="53"/>
+      <c r="F135" s="54"/>
+      <c r="G135" s="53"/>
+      <c r="H135" s="53"/>
+      <c r="I135" s="53"/>
+      <c r="J135" s="54"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="B136" s="50"/>
-      <c r="C136" s="51"/>
-      <c r="D136" s="51"/>
-      <c r="E136" s="51"/>
-      <c r="F136" s="52"/>
-      <c r="G136" s="51"/>
-      <c r="H136" s="51"/>
-      <c r="I136" s="51"/>
-      <c r="J136" s="52"/>
+      <c r="B136" s="52"/>
+      <c r="C136" s="53"/>
+      <c r="D136" s="53"/>
+      <c r="E136" s="53"/>
+      <c r="F136" s="54"/>
+      <c r="G136" s="53"/>
+      <c r="H136" s="53"/>
+      <c r="I136" s="53"/>
+      <c r="J136" s="54"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="B137" s="50"/>
-      <c r="C137" s="51"/>
-      <c r="D137" s="51"/>
-      <c r="E137" s="51"/>
-      <c r="F137" s="52"/>
-      <c r="G137" s="51"/>
-      <c r="H137" s="51"/>
-      <c r="I137" s="51"/>
-      <c r="J137" s="52"/>
+      <c r="B137" s="52"/>
+      <c r="C137" s="53"/>
+      <c r="D137" s="53"/>
+      <c r="E137" s="53"/>
+      <c r="F137" s="54"/>
+      <c r="G137" s="53"/>
+      <c r="H137" s="53"/>
+      <c r="I137" s="53"/>
+      <c r="J137" s="54"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="B138" s="50"/>
-      <c r="C138" s="51"/>
-      <c r="D138" s="51"/>
-      <c r="E138" s="51"/>
-      <c r="F138" s="52"/>
-      <c r="G138" s="51"/>
-      <c r="H138" s="51"/>
-      <c r="I138" s="51"/>
-      <c r="J138" s="52"/>
+      <c r="B138" s="52"/>
+      <c r="C138" s="53"/>
+      <c r="D138" s="53"/>
+      <c r="E138" s="53"/>
+      <c r="F138" s="54"/>
+      <c r="G138" s="53"/>
+      <c r="H138" s="53"/>
+      <c r="I138" s="53"/>
+      <c r="J138" s="54"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="B139" s="50"/>
-      <c r="C139" s="51"/>
-      <c r="D139" s="51"/>
-      <c r="E139" s="51"/>
-      <c r="F139" s="52"/>
-      <c r="G139" s="51"/>
-      <c r="H139" s="51"/>
-      <c r="I139" s="51"/>
-      <c r="J139" s="52"/>
+      <c r="B139" s="52"/>
+      <c r="C139" s="53"/>
+      <c r="D139" s="53"/>
+      <c r="E139" s="53"/>
+      <c r="F139" s="54"/>
+      <c r="G139" s="53"/>
+      <c r="H139" s="53"/>
+      <c r="I139" s="53"/>
+      <c r="J139" s="54"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="B140" s="50"/>
-      <c r="C140" s="51"/>
-      <c r="D140" s="51"/>
-      <c r="E140" s="51"/>
-      <c r="F140" s="52"/>
-      <c r="G140" s="51"/>
-      <c r="H140" s="51"/>
-      <c r="I140" s="51"/>
-      <c r="J140" s="52"/>
+      <c r="B140" s="52"/>
+      <c r="C140" s="53"/>
+      <c r="D140" s="53"/>
+      <c r="E140" s="53"/>
+      <c r="F140" s="54"/>
+      <c r="G140" s="53"/>
+      <c r="H140" s="53"/>
+      <c r="I140" s="53"/>
+      <c r="J140" s="54"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="B141" s="50"/>
-      <c r="C141" s="51"/>
-      <c r="D141" s="51"/>
-      <c r="E141" s="51"/>
-      <c r="F141" s="52"/>
-      <c r="G141" s="51"/>
-      <c r="H141" s="51"/>
-      <c r="I141" s="51"/>
-      <c r="J141" s="52"/>
+      <c r="B141" s="52"/>
+      <c r="C141" s="53"/>
+      <c r="D141" s="53"/>
+      <c r="E141" s="53"/>
+      <c r="F141" s="54"/>
+      <c r="G141" s="53"/>
+      <c r="H141" s="53"/>
+      <c r="I141" s="53"/>
+      <c r="J141" s="54"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="B142" s="50"/>
-      <c r="C142" s="51"/>
-      <c r="D142" s="51"/>
-      <c r="E142" s="51"/>
-      <c r="F142" s="52"/>
-      <c r="G142" s="51"/>
-      <c r="H142" s="51"/>
-      <c r="I142" s="51"/>
-      <c r="J142" s="52"/>
+      <c r="B142" s="52"/>
+      <c r="C142" s="53"/>
+      <c r="D142" s="53"/>
+      <c r="E142" s="53"/>
+      <c r="F142" s="54"/>
+      <c r="G142" s="53"/>
+      <c r="H142" s="53"/>
+      <c r="I142" s="53"/>
+      <c r="J142" s="54"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="B143" s="50"/>
-      <c r="C143" s="51"/>
-      <c r="D143" s="51"/>
-      <c r="E143" s="51"/>
-      <c r="F143" s="52"/>
-      <c r="G143" s="51"/>
-      <c r="H143" s="51"/>
-      <c r="I143" s="51"/>
-      <c r="J143" s="52"/>
+      <c r="B143" s="52"/>
+      <c r="C143" s="53"/>
+      <c r="D143" s="53"/>
+      <c r="E143" s="53"/>
+      <c r="F143" s="54"/>
+      <c r="G143" s="53"/>
+      <c r="H143" s="53"/>
+      <c r="I143" s="53"/>
+      <c r="J143" s="54"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="B144" s="50"/>
-      <c r="C144" s="51"/>
-      <c r="D144" s="51"/>
-      <c r="E144" s="51"/>
-      <c r="F144" s="52"/>
-      <c r="G144" s="51"/>
-      <c r="H144" s="51"/>
-      <c r="I144" s="51"/>
-      <c r="J144" s="52"/>
+      <c r="B144" s="52"/>
+      <c r="C144" s="53"/>
+      <c r="D144" s="53"/>
+      <c r="E144" s="53"/>
+      <c r="F144" s="54"/>
+      <c r="G144" s="53"/>
+      <c r="H144" s="53"/>
+      <c r="I144" s="53"/>
+      <c r="J144" s="54"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="B145" s="50"/>
-      <c r="C145" s="51"/>
-      <c r="D145" s="51"/>
-      <c r="E145" s="51"/>
-      <c r="F145" s="52"/>
-      <c r="G145" s="51"/>
-      <c r="H145" s="51"/>
-      <c r="I145" s="51"/>
-      <c r="J145" s="52"/>
+      <c r="B145" s="52"/>
+      <c r="C145" s="53"/>
+      <c r="D145" s="53"/>
+      <c r="E145" s="53"/>
+      <c r="F145" s="54"/>
+      <c r="G145" s="53"/>
+      <c r="H145" s="53"/>
+      <c r="I145" s="53"/>
+      <c r="J145" s="54"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="B146" s="50"/>
-      <c r="C146" s="51"/>
-      <c r="D146" s="51"/>
-      <c r="E146" s="51"/>
-      <c r="F146" s="52"/>
-      <c r="G146" s="51"/>
-      <c r="H146" s="51"/>
-      <c r="I146" s="51"/>
-      <c r="J146" s="52"/>
+      <c r="B146" s="52"/>
+      <c r="C146" s="53"/>
+      <c r="D146" s="53"/>
+      <c r="E146" s="53"/>
+      <c r="F146" s="54"/>
+      <c r="G146" s="53"/>
+      <c r="H146" s="53"/>
+      <c r="I146" s="53"/>
+      <c r="J146" s="54"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="B147" s="50"/>
-      <c r="C147" s="51"/>
-      <c r="D147" s="51"/>
-      <c r="E147" s="51"/>
-      <c r="F147" s="52"/>
-      <c r="G147" s="51"/>
-      <c r="H147" s="51"/>
-      <c r="I147" s="51"/>
-      <c r="J147" s="52"/>
+      <c r="B147" s="52"/>
+      <c r="C147" s="53"/>
+      <c r="D147" s="53"/>
+      <c r="E147" s="53"/>
+      <c r="F147" s="54"/>
+      <c r="G147" s="53"/>
+      <c r="H147" s="53"/>
+      <c r="I147" s="53"/>
+      <c r="J147" s="54"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="B148" s="50"/>
-      <c r="C148" s="51"/>
-      <c r="D148" s="51"/>
-      <c r="E148" s="51"/>
-      <c r="F148" s="52"/>
-      <c r="G148" s="51"/>
-      <c r="H148" s="51"/>
-      <c r="I148" s="51"/>
-      <c r="J148" s="52"/>
+      <c r="B148" s="52"/>
+      <c r="C148" s="53"/>
+      <c r="D148" s="53"/>
+      <c r="E148" s="53"/>
+      <c r="F148" s="54"/>
+      <c r="G148" s="53"/>
+      <c r="H148" s="53"/>
+      <c r="I148" s="53"/>
+      <c r="J148" s="54"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="B149" s="50"/>
-      <c r="C149" s="51"/>
-      <c r="D149" s="51"/>
-      <c r="E149" s="51"/>
-      <c r="F149" s="52"/>
-      <c r="G149" s="51"/>
-      <c r="H149" s="51"/>
-      <c r="I149" s="51"/>
-      <c r="J149" s="52"/>
+      <c r="B149" s="52"/>
+      <c r="C149" s="53"/>
+      <c r="D149" s="53"/>
+      <c r="E149" s="53"/>
+      <c r="F149" s="54"/>
+      <c r="G149" s="53"/>
+      <c r="H149" s="53"/>
+      <c r="I149" s="53"/>
+      <c r="J149" s="54"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="B150" s="50"/>
-      <c r="C150" s="51"/>
-      <c r="D150" s="51"/>
-      <c r="E150" s="51"/>
-      <c r="F150" s="52"/>
-      <c r="G150" s="51"/>
-      <c r="H150" s="51"/>
-      <c r="I150" s="51"/>
-      <c r="J150" s="52"/>
+      <c r="B150" s="52"/>
+      <c r="C150" s="53"/>
+      <c r="D150" s="53"/>
+      <c r="E150" s="53"/>
+      <c r="F150" s="54"/>
+      <c r="G150" s="53"/>
+      <c r="H150" s="53"/>
+      <c r="I150" s="53"/>
+      <c r="J150" s="54"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="B151" s="50"/>
-      <c r="C151" s="51"/>
-      <c r="D151" s="51"/>
-      <c r="E151" s="51"/>
-      <c r="F151" s="52"/>
-      <c r="G151" s="51"/>
-      <c r="H151" s="51"/>
-      <c r="I151" s="51"/>
-      <c r="J151" s="52"/>
+      <c r="B151" s="52"/>
+      <c r="C151" s="53"/>
+      <c r="D151" s="53"/>
+      <c r="E151" s="53"/>
+      <c r="F151" s="54"/>
+      <c r="G151" s="53"/>
+      <c r="H151" s="53"/>
+      <c r="I151" s="53"/>
+      <c r="J151" s="54"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="B152" s="50"/>
-      <c r="C152" s="51"/>
-      <c r="D152" s="51"/>
-      <c r="E152" s="51"/>
-      <c r="F152" s="52"/>
-      <c r="G152" s="51"/>
-      <c r="H152" s="51"/>
-      <c r="I152" s="51"/>
-      <c r="J152" s="52"/>
+      <c r="B152" s="52"/>
+      <c r="C152" s="53"/>
+      <c r="D152" s="53"/>
+      <c r="E152" s="53"/>
+      <c r="F152" s="54"/>
+      <c r="G152" s="53"/>
+      <c r="H152" s="53"/>
+      <c r="I152" s="53"/>
+      <c r="J152" s="54"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="B153" s="50"/>
-      <c r="C153" s="51"/>
-      <c r="D153" s="51"/>
-      <c r="E153" s="51"/>
-      <c r="F153" s="52"/>
-      <c r="G153" s="51"/>
-      <c r="H153" s="51"/>
-      <c r="I153" s="51"/>
-      <c r="J153" s="52"/>
+      <c r="B153" s="52"/>
+      <c r="C153" s="53"/>
+      <c r="D153" s="53"/>
+      <c r="E153" s="53"/>
+      <c r="F153" s="54"/>
+      <c r="G153" s="53"/>
+      <c r="H153" s="53"/>
+      <c r="I153" s="53"/>
+      <c r="J153" s="54"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="B154" s="50"/>
-      <c r="C154" s="51"/>
-      <c r="D154" s="51"/>
-      <c r="E154" s="51"/>
-      <c r="F154" s="52"/>
-      <c r="G154" s="51"/>
-      <c r="H154" s="51"/>
-      <c r="I154" s="51"/>
-      <c r="J154" s="52"/>
+      <c r="B154" s="52"/>
+      <c r="C154" s="53"/>
+      <c r="D154" s="53"/>
+      <c r="E154" s="53"/>
+      <c r="F154" s="54"/>
+      <c r="G154" s="53"/>
+      <c r="H154" s="53"/>
+      <c r="I154" s="53"/>
+      <c r="J154" s="54"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="B155" s="50"/>
-      <c r="C155" s="51"/>
-      <c r="D155" s="51"/>
-      <c r="E155" s="51"/>
-      <c r="F155" s="52"/>
-      <c r="G155" s="51"/>
-      <c r="H155" s="51"/>
-      <c r="I155" s="51"/>
-      <c r="J155" s="52"/>
+      <c r="B155" s="52"/>
+      <c r="C155" s="53"/>
+      <c r="D155" s="53"/>
+      <c r="E155" s="53"/>
+      <c r="F155" s="54"/>
+      <c r="G155" s="53"/>
+      <c r="H155" s="53"/>
+      <c r="I155" s="53"/>
+      <c r="J155" s="54"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="B156" s="50"/>
-      <c r="C156" s="51"/>
-      <c r="D156" s="51"/>
-      <c r="E156" s="51"/>
-      <c r="F156" s="52"/>
-      <c r="G156" s="51"/>
-      <c r="H156" s="51"/>
-      <c r="I156" s="51"/>
-      <c r="J156" s="52"/>
+      <c r="B156" s="52"/>
+      <c r="C156" s="53"/>
+      <c r="D156" s="53"/>
+      <c r="E156" s="53"/>
+      <c r="F156" s="54"/>
+      <c r="G156" s="53"/>
+      <c r="H156" s="53"/>
+      <c r="I156" s="53"/>
+      <c r="J156" s="54"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="B157" s="50"/>
-      <c r="C157" s="51"/>
-      <c r="D157" s="51"/>
-      <c r="E157" s="51"/>
-      <c r="F157" s="52"/>
-      <c r="G157" s="51"/>
-      <c r="H157" s="51"/>
-      <c r="I157" s="51"/>
-      <c r="J157" s="52"/>
+      <c r="B157" s="52"/>
+      <c r="C157" s="53"/>
+      <c r="D157" s="53"/>
+      <c r="E157" s="53"/>
+      <c r="F157" s="54"/>
+      <c r="G157" s="53"/>
+      <c r="H157" s="53"/>
+      <c r="I157" s="53"/>
+      <c r="J157" s="54"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="B158" s="50"/>
-      <c r="C158" s="51"/>
-      <c r="D158" s="51"/>
-      <c r="E158" s="51"/>
-      <c r="F158" s="52"/>
-      <c r="G158" s="51"/>
-      <c r="H158" s="51"/>
-      <c r="I158" s="51"/>
-      <c r="J158" s="52"/>
+      <c r="B158" s="52"/>
+      <c r="C158" s="53"/>
+      <c r="D158" s="53"/>
+      <c r="E158" s="53"/>
+      <c r="F158" s="54"/>
+      <c r="G158" s="53"/>
+      <c r="H158" s="53"/>
+      <c r="I158" s="53"/>
+      <c r="J158" s="54"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="B159" s="50"/>
-      <c r="C159" s="51"/>
-      <c r="D159" s="51"/>
-      <c r="E159" s="51"/>
-      <c r="F159" s="52"/>
-      <c r="G159" s="51"/>
-      <c r="H159" s="51"/>
-      <c r="I159" s="51"/>
-      <c r="J159" s="52"/>
+      <c r="B159" s="52"/>
+      <c r="C159" s="53"/>
+      <c r="D159" s="53"/>
+      <c r="E159" s="53"/>
+      <c r="F159" s="54"/>
+      <c r="G159" s="53"/>
+      <c r="H159" s="53"/>
+      <c r="I159" s="53"/>
+      <c r="J159" s="54"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="B160" s="50"/>
-      <c r="C160" s="51"/>
-      <c r="D160" s="51"/>
-      <c r="E160" s="51"/>
-      <c r="F160" s="52"/>
-      <c r="G160" s="51"/>
-      <c r="H160" s="51"/>
-      <c r="I160" s="51"/>
-      <c r="J160" s="52"/>
+      <c r="B160" s="52"/>
+      <c r="C160" s="53"/>
+      <c r="D160" s="53"/>
+      <c r="E160" s="53"/>
+      <c r="F160" s="54"/>
+      <c r="G160" s="53"/>
+      <c r="H160" s="53"/>
+      <c r="I160" s="53"/>
+      <c r="J160" s="54"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="B161" s="50"/>
-      <c r="C161" s="51"/>
-      <c r="D161" s="51"/>
-      <c r="E161" s="51"/>
-      <c r="F161" s="52"/>
-      <c r="G161" s="51"/>
-      <c r="H161" s="51"/>
-      <c r="I161" s="51"/>
-      <c r="J161" s="52"/>
+      <c r="B161" s="52"/>
+      <c r="C161" s="53"/>
+      <c r="D161" s="53"/>
+      <c r="E161" s="53"/>
+      <c r="F161" s="54"/>
+      <c r="G161" s="53"/>
+      <c r="H161" s="53"/>
+      <c r="I161" s="53"/>
+      <c r="J161" s="54"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="B162" s="50"/>
-      <c r="C162" s="51"/>
-      <c r="D162" s="51"/>
-      <c r="E162" s="51"/>
-      <c r="F162" s="52"/>
-      <c r="G162" s="51"/>
-      <c r="H162" s="51"/>
-      <c r="I162" s="51"/>
-      <c r="J162" s="52"/>
+      <c r="B162" s="52"/>
+      <c r="C162" s="53"/>
+      <c r="D162" s="53"/>
+      <c r="E162" s="53"/>
+      <c r="F162" s="54"/>
+      <c r="G162" s="53"/>
+      <c r="H162" s="53"/>
+      <c r="I162" s="53"/>
+      <c r="J162" s="54"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="B163" s="50"/>
-      <c r="C163" s="51"/>
-      <c r="D163" s="51"/>
-      <c r="E163" s="51"/>
-      <c r="F163" s="52"/>
-      <c r="G163" s="51"/>
-      <c r="H163" s="51"/>
-      <c r="I163" s="51"/>
-      <c r="J163" s="52"/>
+      <c r="B163" s="52"/>
+      <c r="C163" s="53"/>
+      <c r="D163" s="53"/>
+      <c r="E163" s="53"/>
+      <c r="F163" s="54"/>
+      <c r="G163" s="53"/>
+      <c r="H163" s="53"/>
+      <c r="I163" s="53"/>
+      <c r="J163" s="54"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="B164" s="50"/>
-      <c r="C164" s="51"/>
-      <c r="D164" s="51"/>
-      <c r="E164" s="51"/>
-      <c r="F164" s="52"/>
-      <c r="G164" s="51"/>
-      <c r="H164" s="51"/>
-      <c r="I164" s="51"/>
-      <c r="J164" s="52"/>
+      <c r="B164" s="52"/>
+      <c r="C164" s="53"/>
+      <c r="D164" s="53"/>
+      <c r="E164" s="53"/>
+      <c r="F164" s="54"/>
+      <c r="G164" s="53"/>
+      <c r="H164" s="53"/>
+      <c r="I164" s="53"/>
+      <c r="J164" s="54"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="B165" s="50"/>
-      <c r="C165" s="51"/>
-      <c r="D165" s="51"/>
-      <c r="E165" s="51"/>
-      <c r="F165" s="52"/>
-      <c r="G165" s="51"/>
-      <c r="H165" s="51"/>
-      <c r="I165" s="51"/>
-      <c r="J165" s="52"/>
+      <c r="B165" s="52"/>
+      <c r="C165" s="53"/>
+      <c r="D165" s="53"/>
+      <c r="E165" s="53"/>
+      <c r="F165" s="54"/>
+      <c r="G165" s="53"/>
+      <c r="H165" s="53"/>
+      <c r="I165" s="53"/>
+      <c r="J165" s="54"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="B166" s="50"/>
-      <c r="C166" s="51"/>
-      <c r="D166" s="51"/>
-      <c r="E166" s="51"/>
-      <c r="F166" s="52"/>
-      <c r="G166" s="51"/>
-      <c r="H166" s="51"/>
-      <c r="I166" s="51"/>
-      <c r="J166" s="52"/>
+      <c r="B166" s="52"/>
+      <c r="C166" s="53"/>
+      <c r="D166" s="53"/>
+      <c r="E166" s="53"/>
+      <c r="F166" s="54"/>
+      <c r="G166" s="53"/>
+      <c r="H166" s="53"/>
+      <c r="I166" s="53"/>
+      <c r="J166" s="54"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="B167" s="50"/>
-      <c r="C167" s="51"/>
-      <c r="D167" s="51"/>
-      <c r="E167" s="51"/>
-      <c r="F167" s="52"/>
-      <c r="G167" s="51"/>
-      <c r="H167" s="51"/>
-      <c r="I167" s="51"/>
-      <c r="J167" s="52"/>
+      <c r="B167" s="52"/>
+      <c r="C167" s="53"/>
+      <c r="D167" s="53"/>
+      <c r="E167" s="53"/>
+      <c r="F167" s="54"/>
+      <c r="G167" s="53"/>
+      <c r="H167" s="53"/>
+      <c r="I167" s="53"/>
+      <c r="J167" s="54"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="B168" s="50"/>
-      <c r="C168" s="51"/>
-      <c r="D168" s="51"/>
-      <c r="E168" s="51"/>
-      <c r="F168" s="52"/>
-      <c r="G168" s="51"/>
-      <c r="H168" s="51"/>
-      <c r="I168" s="51"/>
-      <c r="J168" s="52"/>
+      <c r="B168" s="52"/>
+      <c r="C168" s="53"/>
+      <c r="D168" s="53"/>
+      <c r="E168" s="53"/>
+      <c r="F168" s="54"/>
+      <c r="G168" s="53"/>
+      <c r="H168" s="53"/>
+      <c r="I168" s="53"/>
+      <c r="J168" s="54"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="B169" s="50"/>
-      <c r="C169" s="51"/>
-      <c r="D169" s="51"/>
-      <c r="E169" s="51"/>
-      <c r="F169" s="52"/>
-      <c r="G169" s="51"/>
-      <c r="H169" s="51"/>
-      <c r="I169" s="51"/>
-      <c r="J169" s="52"/>
+      <c r="B169" s="52"/>
+      <c r="C169" s="53"/>
+      <c r="D169" s="53"/>
+      <c r="E169" s="53"/>
+      <c r="F169" s="54"/>
+      <c r="G169" s="53"/>
+      <c r="H169" s="53"/>
+      <c r="I169" s="53"/>
+      <c r="J169" s="54"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="B170" s="50"/>
-      <c r="C170" s="51"/>
-      <c r="D170" s="51"/>
-      <c r="E170" s="51"/>
-      <c r="F170" s="52"/>
-      <c r="G170" s="51"/>
-      <c r="H170" s="51"/>
-      <c r="I170" s="51"/>
-      <c r="J170" s="52"/>
+      <c r="B170" s="52"/>
+      <c r="C170" s="53"/>
+      <c r="D170" s="53"/>
+      <c r="E170" s="53"/>
+      <c r="F170" s="54"/>
+      <c r="G170" s="53"/>
+      <c r="H170" s="53"/>
+      <c r="I170" s="53"/>
+      <c r="J170" s="54"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="B171" s="50"/>
-      <c r="C171" s="51"/>
-      <c r="D171" s="51"/>
-      <c r="E171" s="51"/>
-      <c r="F171" s="52"/>
-      <c r="G171" s="51"/>
-      <c r="H171" s="51"/>
-      <c r="I171" s="51"/>
-      <c r="J171" s="52"/>
+      <c r="B171" s="52"/>
+      <c r="C171" s="53"/>
+      <c r="D171" s="53"/>
+      <c r="E171" s="53"/>
+      <c r="F171" s="54"/>
+      <c r="G171" s="53"/>
+      <c r="H171" s="53"/>
+      <c r="I171" s="53"/>
+      <c r="J171" s="54"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="B172" s="50"/>
-      <c r="C172" s="51"/>
-      <c r="D172" s="51"/>
-      <c r="E172" s="51"/>
-      <c r="F172" s="52"/>
-      <c r="G172" s="51"/>
-      <c r="H172" s="51"/>
-      <c r="I172" s="51"/>
-      <c r="J172" s="52"/>
+      <c r="B172" s="52"/>
+      <c r="C172" s="53"/>
+      <c r="D172" s="53"/>
+      <c r="E172" s="53"/>
+      <c r="F172" s="54"/>
+      <c r="G172" s="53"/>
+      <c r="H172" s="53"/>
+      <c r="I172" s="53"/>
+      <c r="J172" s="54"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="B173" s="50"/>
-      <c r="C173" s="51"/>
-      <c r="D173" s="51"/>
-      <c r="E173" s="51"/>
-      <c r="F173" s="52"/>
-      <c r="G173" s="51"/>
-      <c r="H173" s="51"/>
-      <c r="I173" s="51"/>
-      <c r="J173" s="52"/>
+      <c r="B173" s="52"/>
+      <c r="C173" s="53"/>
+      <c r="D173" s="53"/>
+      <c r="E173" s="53"/>
+      <c r="F173" s="54"/>
+      <c r="G173" s="53"/>
+      <c r="H173" s="53"/>
+      <c r="I173" s="53"/>
+      <c r="J173" s="54"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="B174" s="50"/>
-      <c r="C174" s="51"/>
-      <c r="D174" s="51"/>
-      <c r="E174" s="51"/>
-      <c r="F174" s="52"/>
-      <c r="G174" s="51"/>
-      <c r="H174" s="51"/>
-      <c r="I174" s="51"/>
-      <c r="J174" s="52"/>
+      <c r="B174" s="52"/>
+      <c r="C174" s="53"/>
+      <c r="D174" s="53"/>
+      <c r="E174" s="53"/>
+      <c r="F174" s="54"/>
+      <c r="G174" s="53"/>
+      <c r="H174" s="53"/>
+      <c r="I174" s="53"/>
+      <c r="J174" s="54"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="B175" s="50"/>
-      <c r="C175" s="51"/>
-      <c r="D175" s="51"/>
-      <c r="E175" s="51"/>
-      <c r="F175" s="52"/>
-      <c r="G175" s="51"/>
-      <c r="H175" s="51"/>
-      <c r="I175" s="51"/>
-      <c r="J175" s="52"/>
+      <c r="B175" s="52"/>
+      <c r="C175" s="53"/>
+      <c r="D175" s="53"/>
+      <c r="E175" s="53"/>
+      <c r="F175" s="54"/>
+      <c r="G175" s="53"/>
+      <c r="H175" s="53"/>
+      <c r="I175" s="53"/>
+      <c r="J175" s="54"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="B176" s="50"/>
-      <c r="C176" s="51"/>
-      <c r="D176" s="51"/>
-      <c r="E176" s="51"/>
-      <c r="F176" s="52"/>
-      <c r="G176" s="51"/>
-      <c r="H176" s="51"/>
-      <c r="I176" s="51"/>
-      <c r="J176" s="52"/>
+      <c r="B176" s="52"/>
+      <c r="C176" s="53"/>
+      <c r="D176" s="53"/>
+      <c r="E176" s="53"/>
+      <c r="F176" s="54"/>
+      <c r="G176" s="53"/>
+      <c r="H176" s="53"/>
+      <c r="I176" s="53"/>
+      <c r="J176" s="54"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="B177" s="50"/>
-      <c r="C177" s="51"/>
-      <c r="D177" s="51"/>
-      <c r="E177" s="51"/>
-      <c r="F177" s="52"/>
-      <c r="G177" s="51"/>
-      <c r="H177" s="51"/>
-      <c r="I177" s="51"/>
-      <c r="J177" s="52"/>
+      <c r="B177" s="52"/>
+      <c r="C177" s="53"/>
+      <c r="D177" s="53"/>
+      <c r="E177" s="53"/>
+      <c r="F177" s="54"/>
+      <c r="G177" s="53"/>
+      <c r="H177" s="53"/>
+      <c r="I177" s="53"/>
+      <c r="J177" s="54"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="B178" s="50"/>
-      <c r="C178" s="51"/>
-      <c r="D178" s="51"/>
-      <c r="E178" s="51"/>
-      <c r="F178" s="52"/>
-      <c r="G178" s="51"/>
-      <c r="H178" s="51"/>
-      <c r="I178" s="51"/>
-      <c r="J178" s="52"/>
+      <c r="B178" s="52"/>
+      <c r="C178" s="53"/>
+      <c r="D178" s="53"/>
+      <c r="E178" s="53"/>
+      <c r="F178" s="54"/>
+      <c r="G178" s="53"/>
+      <c r="H178" s="53"/>
+      <c r="I178" s="53"/>
+      <c r="J178" s="54"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="B179" s="50"/>
-      <c r="C179" s="51"/>
-      <c r="D179" s="51"/>
-      <c r="E179" s="51"/>
-      <c r="F179" s="52"/>
-      <c r="G179" s="51"/>
-      <c r="H179" s="51"/>
-      <c r="I179" s="51"/>
-      <c r="J179" s="52"/>
+      <c r="B179" s="52"/>
+      <c r="C179" s="53"/>
+      <c r="D179" s="53"/>
+      <c r="E179" s="53"/>
+      <c r="F179" s="54"/>
+      <c r="G179" s="53"/>
+      <c r="H179" s="53"/>
+      <c r="I179" s="53"/>
+      <c r="J179" s="54"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="B180" s="50"/>
-      <c r="C180" s="51"/>
-      <c r="D180" s="51"/>
-      <c r="E180" s="51"/>
-      <c r="F180" s="52"/>
-      <c r="G180" s="51"/>
-      <c r="H180" s="51"/>
-      <c r="I180" s="51"/>
-      <c r="J180" s="52"/>
+      <c r="B180" s="52"/>
+      <c r="C180" s="53"/>
+      <c r="D180" s="53"/>
+      <c r="E180" s="53"/>
+      <c r="F180" s="54"/>
+      <c r="G180" s="53"/>
+      <c r="H180" s="53"/>
+      <c r="I180" s="53"/>
+      <c r="J180" s="54"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="B181" s="50"/>
-      <c r="C181" s="51"/>
-      <c r="D181" s="51"/>
-      <c r="E181" s="51"/>
-      <c r="F181" s="52"/>
-      <c r="G181" s="51"/>
-      <c r="H181" s="51"/>
-      <c r="I181" s="51"/>
-      <c r="J181" s="52"/>
+      <c r="B181" s="52"/>
+      <c r="C181" s="53"/>
+      <c r="D181" s="53"/>
+      <c r="E181" s="53"/>
+      <c r="F181" s="54"/>
+      <c r="G181" s="53"/>
+      <c r="H181" s="53"/>
+      <c r="I181" s="53"/>
+      <c r="J181" s="54"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="B182" s="50"/>
-      <c r="C182" s="51"/>
-      <c r="D182" s="51"/>
-      <c r="E182" s="51"/>
-      <c r="F182" s="52"/>
-      <c r="G182" s="51"/>
-      <c r="H182" s="51"/>
-      <c r="I182" s="51"/>
-      <c r="J182" s="52"/>
+      <c r="B182" s="52"/>
+      <c r="C182" s="53"/>
+      <c r="D182" s="53"/>
+      <c r="E182" s="53"/>
+      <c r="F182" s="54"/>
+      <c r="G182" s="53"/>
+      <c r="H182" s="53"/>
+      <c r="I182" s="53"/>
+      <c r="J182" s="54"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="B183" s="50"/>
-      <c r="C183" s="51"/>
-      <c r="D183" s="51"/>
-      <c r="E183" s="51"/>
-      <c r="F183" s="52"/>
-      <c r="G183" s="51"/>
-      <c r="H183" s="51"/>
-      <c r="I183" s="51"/>
-      <c r="J183" s="52"/>
+      <c r="B183" s="52"/>
+      <c r="C183" s="53"/>
+      <c r="D183" s="53"/>
+      <c r="E183" s="53"/>
+      <c r="F183" s="54"/>
+      <c r="G183" s="53"/>
+      <c r="H183" s="53"/>
+      <c r="I183" s="53"/>
+      <c r="J183" s="54"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="B184" s="50"/>
-      <c r="C184" s="51"/>
-      <c r="D184" s="51"/>
-      <c r="E184" s="51"/>
-      <c r="F184" s="52"/>
-      <c r="G184" s="51"/>
-      <c r="H184" s="51"/>
-      <c r="I184" s="51"/>
-      <c r="J184" s="52"/>
+      <c r="B184" s="52"/>
+      <c r="C184" s="53"/>
+      <c r="D184" s="53"/>
+      <c r="E184" s="53"/>
+      <c r="F184" s="54"/>
+      <c r="G184" s="53"/>
+      <c r="H184" s="53"/>
+      <c r="I184" s="53"/>
+      <c r="J184" s="54"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="B185" s="50"/>
-      <c r="C185" s="51"/>
-      <c r="D185" s="51"/>
-      <c r="E185" s="51"/>
-      <c r="F185" s="52"/>
-      <c r="G185" s="51"/>
-      <c r="H185" s="51"/>
-      <c r="I185" s="51"/>
-      <c r="J185" s="52"/>
+      <c r="B185" s="52"/>
+      <c r="C185" s="53"/>
+      <c r="D185" s="53"/>
+      <c r="E185" s="53"/>
+      <c r="F185" s="54"/>
+      <c r="G185" s="53"/>
+      <c r="H185" s="53"/>
+      <c r="I185" s="53"/>
+      <c r="J185" s="54"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="B186" s="50"/>
-      <c r="C186" s="51"/>
-      <c r="D186" s="51"/>
-      <c r="E186" s="51"/>
-      <c r="F186" s="52"/>
-      <c r="G186" s="51"/>
-      <c r="H186" s="51"/>
-      <c r="I186" s="51"/>
-      <c r="J186" s="52"/>
+      <c r="B186" s="52"/>
+      <c r="C186" s="53"/>
+      <c r="D186" s="53"/>
+      <c r="E186" s="53"/>
+      <c r="F186" s="54"/>
+      <c r="G186" s="53"/>
+      <c r="H186" s="53"/>
+      <c r="I186" s="53"/>
+      <c r="J186" s="54"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="B187" s="50"/>
-      <c r="C187" s="51"/>
-      <c r="D187" s="51"/>
-      <c r="E187" s="51"/>
-      <c r="F187" s="52"/>
-      <c r="G187" s="51"/>
-      <c r="H187" s="51"/>
-      <c r="I187" s="51"/>
-      <c r="J187" s="52"/>
+      <c r="B187" s="52"/>
+      <c r="C187" s="53"/>
+      <c r="D187" s="53"/>
+      <c r="E187" s="53"/>
+      <c r="F187" s="54"/>
+      <c r="G187" s="53"/>
+      <c r="H187" s="53"/>
+      <c r="I187" s="53"/>
+      <c r="J187" s="54"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="B188" s="50"/>
-      <c r="C188" s="51"/>
-      <c r="D188" s="51"/>
-      <c r="E188" s="51"/>
-      <c r="F188" s="52"/>
-      <c r="G188" s="51"/>
-      <c r="H188" s="51"/>
-      <c r="I188" s="51"/>
-      <c r="J188" s="52"/>
+      <c r="B188" s="52"/>
+      <c r="C188" s="53"/>
+      <c r="D188" s="53"/>
+      <c r="E188" s="53"/>
+      <c r="F188" s="54"/>
+      <c r="G188" s="53"/>
+      <c r="H188" s="53"/>
+      <c r="I188" s="53"/>
+      <c r="J188" s="54"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="B189" s="50"/>
-      <c r="C189" s="51"/>
-      <c r="D189" s="51"/>
-      <c r="E189" s="51"/>
-      <c r="F189" s="52"/>
-      <c r="G189" s="51"/>
-      <c r="H189" s="51"/>
-      <c r="I189" s="51"/>
-      <c r="J189" s="52"/>
+      <c r="B189" s="52"/>
+      <c r="C189" s="53"/>
+      <c r="D189" s="53"/>
+      <c r="E189" s="53"/>
+      <c r="F189" s="54"/>
+      <c r="G189" s="53"/>
+      <c r="H189" s="53"/>
+      <c r="I189" s="53"/>
+      <c r="J189" s="54"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="B190" s="50"/>
-      <c r="C190" s="51"/>
-      <c r="D190" s="51"/>
-      <c r="E190" s="51"/>
-      <c r="F190" s="52"/>
-      <c r="G190" s="51"/>
-      <c r="H190" s="51"/>
-      <c r="I190" s="51"/>
-      <c r="J190" s="52"/>
+      <c r="B190" s="52"/>
+      <c r="C190" s="53"/>
+      <c r="D190" s="53"/>
+      <c r="E190" s="53"/>
+      <c r="F190" s="54"/>
+      <c r="G190" s="53"/>
+      <c r="H190" s="53"/>
+      <c r="I190" s="53"/>
+      <c r="J190" s="54"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="B191" s="50"/>
-      <c r="C191" s="51"/>
-      <c r="D191" s="51"/>
-      <c r="E191" s="51"/>
-      <c r="F191" s="52"/>
-      <c r="G191" s="51"/>
-      <c r="H191" s="51"/>
-      <c r="I191" s="51"/>
-      <c r="J191" s="52"/>
+      <c r="B191" s="52"/>
+      <c r="C191" s="53"/>
+      <c r="D191" s="53"/>
+      <c r="E191" s="53"/>
+      <c r="F191" s="54"/>
+      <c r="G191" s="53"/>
+      <c r="H191" s="53"/>
+      <c r="I191" s="53"/>
+      <c r="J191" s="54"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="B192" s="50"/>
-      <c r="C192" s="51"/>
-      <c r="D192" s="51"/>
-      <c r="E192" s="51"/>
-      <c r="F192" s="52"/>
-      <c r="G192" s="51"/>
-      <c r="H192" s="51"/>
-      <c r="I192" s="51"/>
-      <c r="J192" s="52"/>
+      <c r="B192" s="52"/>
+      <c r="C192" s="53"/>
+      <c r="D192" s="53"/>
+      <c r="E192" s="53"/>
+      <c r="F192" s="54"/>
+      <c r="G192" s="53"/>
+      <c r="H192" s="53"/>
+      <c r="I192" s="53"/>
+      <c r="J192" s="54"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="B193" s="50"/>
-      <c r="C193" s="51"/>
-      <c r="D193" s="51"/>
-      <c r="E193" s="51"/>
-      <c r="F193" s="52"/>
-      <c r="G193" s="51"/>
-      <c r="H193" s="51"/>
-      <c r="I193" s="51"/>
-      <c r="J193" s="52"/>
+      <c r="B193" s="52"/>
+      <c r="C193" s="53"/>
+      <c r="D193" s="53"/>
+      <c r="E193" s="53"/>
+      <c r="F193" s="54"/>
+      <c r="G193" s="53"/>
+      <c r="H193" s="53"/>
+      <c r="I193" s="53"/>
+      <c r="J193" s="54"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="B194" s="50"/>
-      <c r="C194" s="51"/>
-      <c r="D194" s="51"/>
-      <c r="E194" s="51"/>
-      <c r="F194" s="52"/>
-      <c r="G194" s="51"/>
-      <c r="H194" s="51"/>
-      <c r="I194" s="51"/>
-      <c r="J194" s="52"/>
+      <c r="B194" s="52"/>
+      <c r="C194" s="53"/>
+      <c r="D194" s="53"/>
+      <c r="E194" s="53"/>
+      <c r="F194" s="54"/>
+      <c r="G194" s="53"/>
+      <c r="H194" s="53"/>
+      <c r="I194" s="53"/>
+      <c r="J194" s="54"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="B195" s="50"/>
-      <c r="C195" s="51"/>
-      <c r="D195" s="51"/>
-      <c r="E195" s="51"/>
-      <c r="F195" s="52"/>
-      <c r="G195" s="51"/>
-      <c r="H195" s="51"/>
-      <c r="I195" s="51"/>
-      <c r="J195" s="52"/>
+      <c r="B195" s="52"/>
+      <c r="C195" s="53"/>
+      <c r="D195" s="53"/>
+      <c r="E195" s="53"/>
+      <c r="F195" s="54"/>
+      <c r="G195" s="53"/>
+      <c r="H195" s="53"/>
+      <c r="I195" s="53"/>
+      <c r="J195" s="54"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="B196" s="50"/>
-      <c r="C196" s="51"/>
-      <c r="D196" s="51"/>
-      <c r="E196" s="51"/>
-      <c r="F196" s="52"/>
-      <c r="G196" s="51"/>
-      <c r="H196" s="51"/>
-      <c r="I196" s="51"/>
-      <c r="J196" s="52"/>
+      <c r="B196" s="52"/>
+      <c r="C196" s="53"/>
+      <c r="D196" s="53"/>
+      <c r="E196" s="53"/>
+      <c r="F196" s="54"/>
+      <c r="G196" s="53"/>
+      <c r="H196" s="53"/>
+      <c r="I196" s="53"/>
+      <c r="J196" s="54"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="B197" s="50"/>
-      <c r="C197" s="51"/>
-      <c r="D197" s="51"/>
-      <c r="E197" s="51"/>
-      <c r="F197" s="52"/>
-      <c r="G197" s="51"/>
-      <c r="H197" s="51"/>
-      <c r="I197" s="51"/>
-      <c r="J197" s="52"/>
+      <c r="B197" s="52"/>
+      <c r="C197" s="53"/>
+      <c r="D197" s="53"/>
+      <c r="E197" s="53"/>
+      <c r="F197" s="54"/>
+      <c r="G197" s="53"/>
+      <c r="H197" s="53"/>
+      <c r="I197" s="53"/>
+      <c r="J197" s="54"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="B198" s="50"/>
-      <c r="C198" s="51"/>
-      <c r="D198" s="51"/>
-      <c r="E198" s="51"/>
-      <c r="F198" s="52"/>
-      <c r="G198" s="51"/>
-      <c r="H198" s="51"/>
-      <c r="I198" s="51"/>
-      <c r="J198" s="52"/>
+      <c r="B198" s="52"/>
+      <c r="C198" s="53"/>
+      <c r="D198" s="53"/>
+      <c r="E198" s="53"/>
+      <c r="F198" s="54"/>
+      <c r="G198" s="53"/>
+      <c r="H198" s="53"/>
+      <c r="I198" s="53"/>
+      <c r="J198" s="54"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="B199" s="50"/>
-      <c r="C199" s="51"/>
-      <c r="D199" s="51"/>
-      <c r="E199" s="51"/>
-      <c r="F199" s="52"/>
-      <c r="G199" s="51"/>
-      <c r="H199" s="51"/>
-      <c r="I199" s="51"/>
-      <c r="J199" s="52"/>
+      <c r="B199" s="52"/>
+      <c r="C199" s="53"/>
+      <c r="D199" s="53"/>
+      <c r="E199" s="53"/>
+      <c r="F199" s="54"/>
+      <c r="G199" s="53"/>
+      <c r="H199" s="53"/>
+      <c r="I199" s="53"/>
+      <c r="J199" s="54"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="B200" s="50"/>
-      <c r="C200" s="51"/>
-      <c r="D200" s="51"/>
-      <c r="E200" s="51"/>
-      <c r="F200" s="52"/>
-      <c r="G200" s="51"/>
-      <c r="H200" s="51"/>
-      <c r="I200" s="51"/>
-      <c r="J200" s="52"/>
+      <c r="B200" s="52"/>
+      <c r="C200" s="53"/>
+      <c r="D200" s="53"/>
+      <c r="E200" s="53"/>
+      <c r="F200" s="54"/>
+      <c r="G200" s="53"/>
+      <c r="H200" s="53"/>
+      <c r="I200" s="53"/>
+      <c r="J200" s="54"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="B201" s="50"/>
-      <c r="C201" s="51"/>
-      <c r="D201" s="51"/>
-      <c r="E201" s="51"/>
-      <c r="F201" s="52"/>
-      <c r="G201" s="51"/>
-      <c r="H201" s="51"/>
-      <c r="I201" s="51"/>
-      <c r="J201" s="52"/>
+      <c r="B201" s="52"/>
+      <c r="C201" s="53"/>
+      <c r="D201" s="53"/>
+      <c r="E201" s="53"/>
+      <c r="F201" s="54"/>
+      <c r="G201" s="53"/>
+      <c r="H201" s="53"/>
+      <c r="I201" s="53"/>
+      <c r="J201" s="54"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="B202" s="50"/>
-      <c r="C202" s="51"/>
-      <c r="D202" s="51"/>
-      <c r="E202" s="51"/>
-      <c r="F202" s="52"/>
-      <c r="G202" s="51"/>
-      <c r="H202" s="51"/>
-      <c r="I202" s="51"/>
-      <c r="J202" s="52"/>
+      <c r="B202" s="52"/>
+      <c r="C202" s="53"/>
+      <c r="D202" s="53"/>
+      <c r="E202" s="53"/>
+      <c r="F202" s="54"/>
+      <c r="G202" s="53"/>
+      <c r="H202" s="53"/>
+      <c r="I202" s="53"/>
+      <c r="J202" s="54"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="B203" s="50"/>
-      <c r="C203" s="51"/>
-      <c r="D203" s="51"/>
-      <c r="E203" s="51"/>
-      <c r="F203" s="52"/>
-      <c r="G203" s="51"/>
-      <c r="H203" s="51"/>
-      <c r="I203" s="51"/>
-      <c r="J203" s="52"/>
+      <c r="B203" s="52"/>
+      <c r="C203" s="53"/>
+      <c r="D203" s="53"/>
+      <c r="E203" s="53"/>
+      <c r="F203" s="54"/>
+      <c r="G203" s="53"/>
+      <c r="H203" s="53"/>
+      <c r="I203" s="53"/>
+      <c r="J203" s="54"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="B204" s="50"/>
-      <c r="C204" s="51"/>
-      <c r="D204" s="51"/>
-      <c r="E204" s="51"/>
-      <c r="F204" s="52"/>
-      <c r="G204" s="51"/>
-      <c r="H204" s="51"/>
-      <c r="I204" s="51"/>
-      <c r="J204" s="52"/>
+      <c r="B204" s="52"/>
+      <c r="C204" s="53"/>
+      <c r="D204" s="53"/>
+      <c r="E204" s="53"/>
+      <c r="F204" s="54"/>
+      <c r="G204" s="53"/>
+      <c r="H204" s="53"/>
+      <c r="I204" s="53"/>
+      <c r="J204" s="54"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="B205" s="50"/>
-      <c r="C205" s="51"/>
-      <c r="D205" s="51"/>
-      <c r="E205" s="51"/>
-      <c r="F205" s="52"/>
-      <c r="G205" s="51"/>
-      <c r="H205" s="51"/>
-      <c r="I205" s="51"/>
-      <c r="J205" s="52"/>
+      <c r="B205" s="52"/>
+      <c r="C205" s="53"/>
+      <c r="D205" s="53"/>
+      <c r="E205" s="53"/>
+      <c r="F205" s="54"/>
+      <c r="G205" s="53"/>
+      <c r="H205" s="53"/>
+      <c r="I205" s="53"/>
+      <c r="J205" s="54"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="B206" s="50"/>
-      <c r="C206" s="51"/>
-      <c r="D206" s="51"/>
-      <c r="E206" s="51"/>
-      <c r="F206" s="52"/>
-      <c r="G206" s="51"/>
-      <c r="H206" s="51"/>
-      <c r="I206" s="51"/>
-      <c r="J206" s="52"/>
+      <c r="B206" s="52"/>
+      <c r="C206" s="53"/>
+      <c r="D206" s="53"/>
+      <c r="E206" s="53"/>
+      <c r="F206" s="54"/>
+      <c r="G206" s="53"/>
+      <c r="H206" s="53"/>
+      <c r="I206" s="53"/>
+      <c r="J206" s="54"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="B207" s="50"/>
-      <c r="C207" s="51"/>
-      <c r="D207" s="51"/>
-      <c r="E207" s="51"/>
-      <c r="F207" s="52"/>
-      <c r="G207" s="51"/>
-      <c r="H207" s="51"/>
-      <c r="I207" s="51"/>
-      <c r="J207" s="52"/>
+      <c r="B207" s="52"/>
+      <c r="C207" s="53"/>
+      <c r="D207" s="53"/>
+      <c r="E207" s="53"/>
+      <c r="F207" s="54"/>
+      <c r="G207" s="53"/>
+      <c r="H207" s="53"/>
+      <c r="I207" s="53"/>
+      <c r="J207" s="54"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="B208" s="50"/>
-      <c r="C208" s="51"/>
-      <c r="D208" s="51"/>
-      <c r="E208" s="51"/>
-      <c r="F208" s="52"/>
-      <c r="G208" s="51"/>
-      <c r="H208" s="51"/>
-      <c r="I208" s="51"/>
-      <c r="J208" s="52"/>
+      <c r="B208" s="52"/>
+      <c r="C208" s="53"/>
+      <c r="D208" s="53"/>
+      <c r="E208" s="53"/>
+      <c r="F208" s="54"/>
+      <c r="G208" s="53"/>
+      <c r="H208" s="53"/>
+      <c r="I208" s="53"/>
+      <c r="J208" s="54"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="B209" s="50"/>
-      <c r="C209" s="51"/>
-      <c r="D209" s="51"/>
-      <c r="E209" s="51"/>
-      <c r="F209" s="52"/>
-      <c r="G209" s="51"/>
-      <c r="H209" s="51"/>
-      <c r="I209" s="51"/>
-      <c r="J209" s="52"/>
+      <c r="B209" s="52"/>
+      <c r="C209" s="53"/>
+      <c r="D209" s="53"/>
+      <c r="E209" s="53"/>
+      <c r="F209" s="54"/>
+      <c r="G209" s="53"/>
+      <c r="H209" s="53"/>
+      <c r="I209" s="53"/>
+      <c r="J209" s="54"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="B210" s="50"/>
-      <c r="C210" s="51"/>
-      <c r="D210" s="51"/>
-      <c r="E210" s="51"/>
-      <c r="F210" s="52"/>
-      <c r="G210" s="51"/>
-      <c r="H210" s="51"/>
-      <c r="I210" s="51"/>
-      <c r="J210" s="52"/>
+      <c r="B210" s="52"/>
+      <c r="C210" s="53"/>
+      <c r="D210" s="53"/>
+      <c r="E210" s="53"/>
+      <c r="F210" s="54"/>
+      <c r="G210" s="53"/>
+      <c r="H210" s="53"/>
+      <c r="I210" s="53"/>
+      <c r="J210" s="54"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="B211" s="50"/>
-      <c r="C211" s="51"/>
-      <c r="D211" s="51"/>
-      <c r="E211" s="51"/>
-      <c r="F211" s="52"/>
-      <c r="G211" s="51"/>
-      <c r="H211" s="51"/>
-      <c r="I211" s="51"/>
-      <c r="J211" s="52"/>
+      <c r="B211" s="52"/>
+      <c r="C211" s="53"/>
+      <c r="D211" s="53"/>
+      <c r="E211" s="53"/>
+      <c r="F211" s="54"/>
+      <c r="G211" s="53"/>
+      <c r="H211" s="53"/>
+      <c r="I211" s="53"/>
+      <c r="J211" s="54"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="B212" s="50"/>
-      <c r="C212" s="51"/>
-      <c r="D212" s="51"/>
-      <c r="E212" s="51"/>
-      <c r="F212" s="52"/>
-      <c r="G212" s="51"/>
-      <c r="H212" s="51"/>
-      <c r="I212" s="51"/>
-      <c r="J212" s="52"/>
+      <c r="B212" s="52"/>
+      <c r="C212" s="53"/>
+      <c r="D212" s="53"/>
+      <c r="E212" s="53"/>
+      <c r="F212" s="54"/>
+      <c r="G212" s="53"/>
+      <c r="H212" s="53"/>
+      <c r="I212" s="53"/>
+      <c r="J212" s="54"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="B213" s="50"/>
-      <c r="C213" s="51"/>
-      <c r="D213" s="51"/>
-      <c r="E213" s="51"/>
-      <c r="F213" s="52"/>
-      <c r="G213" s="51"/>
-      <c r="H213" s="51"/>
-      <c r="I213" s="51"/>
-      <c r="J213" s="52"/>
+      <c r="B213" s="52"/>
+      <c r="C213" s="53"/>
+      <c r="D213" s="53"/>
+      <c r="E213" s="53"/>
+      <c r="F213" s="54"/>
+      <c r="G213" s="53"/>
+      <c r="H213" s="53"/>
+      <c r="I213" s="53"/>
+      <c r="J213" s="54"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="B214" s="50"/>
-      <c r="C214" s="51"/>
-      <c r="D214" s="51"/>
-      <c r="E214" s="51"/>
-      <c r="F214" s="52"/>
-      <c r="G214" s="51"/>
-      <c r="H214" s="51"/>
-      <c r="I214" s="51"/>
-      <c r="J214" s="52"/>
+      <c r="B214" s="52"/>
+      <c r="C214" s="53"/>
+      <c r="D214" s="53"/>
+      <c r="E214" s="53"/>
+      <c r="F214" s="54"/>
+      <c r="G214" s="53"/>
+      <c r="H214" s="53"/>
+      <c r="I214" s="53"/>
+      <c r="J214" s="54"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="B215" s="50"/>
-      <c r="C215" s="51"/>
-      <c r="D215" s="51"/>
-      <c r="E215" s="51"/>
-      <c r="F215" s="52"/>
-      <c r="G215" s="51"/>
-      <c r="H215" s="51"/>
-      <c r="I215" s="51"/>
-      <c r="J215" s="52"/>
+      <c r="B215" s="52"/>
+      <c r="C215" s="53"/>
+      <c r="D215" s="53"/>
+      <c r="E215" s="53"/>
+      <c r="F215" s="54"/>
+      <c r="G215" s="53"/>
+      <c r="H215" s="53"/>
+      <c r="I215" s="53"/>
+      <c r="J215" s="54"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="B216" s="50"/>
-      <c r="C216" s="51"/>
-      <c r="D216" s="51"/>
-      <c r="E216" s="51"/>
-      <c r="F216" s="52"/>
-      <c r="G216" s="51"/>
-      <c r="H216" s="51"/>
-      <c r="I216" s="51"/>
-      <c r="J216" s="52"/>
+      <c r="B216" s="52"/>
+      <c r="C216" s="53"/>
+      <c r="D216" s="53"/>
+      <c r="E216" s="53"/>
+      <c r="F216" s="54"/>
+      <c r="G216" s="53"/>
+      <c r="H216" s="53"/>
+      <c r="I216" s="53"/>
+      <c r="J216" s="54"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="B217" s="50"/>
-      <c r="C217" s="51"/>
-      <c r="D217" s="51"/>
-      <c r="E217" s="51"/>
-      <c r="F217" s="52"/>
-      <c r="G217" s="51"/>
-      <c r="H217" s="51"/>
-      <c r="I217" s="51"/>
-      <c r="J217" s="52"/>
+      <c r="B217" s="52"/>
+      <c r="C217" s="53"/>
+      <c r="D217" s="53"/>
+      <c r="E217" s="53"/>
+      <c r="F217" s="54"/>
+      <c r="G217" s="53"/>
+      <c r="H217" s="53"/>
+      <c r="I217" s="53"/>
+      <c r="J217" s="54"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="B218" s="50"/>
-      <c r="C218" s="51"/>
-      <c r="D218" s="51"/>
-      <c r="E218" s="51"/>
-      <c r="F218" s="52"/>
-      <c r="G218" s="51"/>
-      <c r="H218" s="51"/>
-      <c r="I218" s="51"/>
-      <c r="J218" s="52"/>
+      <c r="B218" s="52"/>
+      <c r="C218" s="53"/>
+      <c r="D218" s="53"/>
+      <c r="E218" s="53"/>
+      <c r="F218" s="54"/>
+      <c r="G218" s="53"/>
+      <c r="H218" s="53"/>
+      <c r="I218" s="53"/>
+      <c r="J218" s="54"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="B219" s="50"/>
-      <c r="C219" s="51"/>
-      <c r="D219" s="51"/>
-      <c r="E219" s="51"/>
-      <c r="F219" s="52"/>
-      <c r="G219" s="51"/>
-      <c r="H219" s="51"/>
-      <c r="I219" s="51"/>
-      <c r="J219" s="52"/>
+      <c r="B219" s="52"/>
+      <c r="C219" s="53"/>
+      <c r="D219" s="53"/>
+      <c r="E219" s="53"/>
+      <c r="F219" s="54"/>
+      <c r="G219" s="53"/>
+      <c r="H219" s="53"/>
+      <c r="I219" s="53"/>
+      <c r="J219" s="54"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="B220" s="50"/>
-      <c r="C220" s="51"/>
-      <c r="D220" s="51"/>
-      <c r="E220" s="51"/>
-      <c r="F220" s="52"/>
-      <c r="G220" s="51"/>
-      <c r="H220" s="51"/>
-      <c r="I220" s="51"/>
-      <c r="J220" s="52"/>
+      <c r="B220" s="52"/>
+      <c r="C220" s="53"/>
+      <c r="D220" s="53"/>
+      <c r="E220" s="53"/>
+      <c r="F220" s="54"/>
+      <c r="G220" s="53"/>
+      <c r="H220" s="53"/>
+      <c r="I220" s="53"/>
+      <c r="J220" s="54"/>
     </row>
     <row r="221" ht="15.75" customHeight="1">
-      <c r="B221" s="50"/>
-      <c r="C221" s="51"/>
-      <c r="D221" s="51"/>
-      <c r="E221" s="51"/>
-      <c r="F221" s="52"/>
-      <c r="G221" s="51"/>
-      <c r="H221" s="51"/>
-      <c r="I221" s="51"/>
-      <c r="J221" s="52"/>
+      <c r="B221" s="52"/>
+      <c r="C221" s="53"/>
+      <c r="D221" s="53"/>
+      <c r="E221" s="53"/>
+      <c r="F221" s="54"/>
+      <c r="G221" s="53"/>
+      <c r="H221" s="53"/>
+      <c r="I221" s="53"/>
+      <c r="J221" s="54"/>
     </row>
     <row r="222" ht="15.75" customHeight="1">
-      <c r="B222" s="50"/>
-      <c r="C222" s="51"/>
-      <c r="D222" s="51"/>
-      <c r="E222" s="51"/>
-      <c r="F222" s="52"/>
-      <c r="G222" s="51"/>
-      <c r="H222" s="51"/>
-      <c r="I222" s="51"/>
-      <c r="J222" s="52"/>
+      <c r="B222" s="52"/>
+      <c r="C222" s="53"/>
+      <c r="D222" s="53"/>
+      <c r="E222" s="53"/>
+      <c r="F222" s="54"/>
+      <c r="G222" s="53"/>
+      <c r="H222" s="53"/>
+      <c r="I222" s="53"/>
+      <c r="J222" s="54"/>
     </row>
     <row r="223" ht="15.75" customHeight="1">
-      <c r="B223" s="50"/>
-      <c r="C223" s="51"/>
-      <c r="D223" s="51"/>
-      <c r="E223" s="51"/>
-      <c r="F223" s="52"/>
-      <c r="G223" s="51"/>
-      <c r="H223" s="51"/>
-      <c r="I223" s="51"/>
-      <c r="J223" s="52"/>
+      <c r="B223" s="52"/>
+      <c r="C223" s="53"/>
+      <c r="D223" s="53"/>
+      <c r="E223" s="53"/>
+      <c r="F223" s="54"/>
+      <c r="G223" s="53"/>
+      <c r="H223" s="53"/>
+      <c r="I223" s="53"/>
+      <c r="J223" s="54"/>
     </row>
     <row r="224" ht="15.75" customHeight="1">
-      <c r="B224" s="50"/>
-      <c r="C224" s="51"/>
-      <c r="D224" s="51"/>
-      <c r="E224" s="51"/>
-      <c r="F224" s="52"/>
-      <c r="G224" s="51"/>
-      <c r="H224" s="51"/>
-      <c r="I224" s="51"/>
-      <c r="J224" s="52"/>
+      <c r="B224" s="52"/>
+      <c r="C224" s="53"/>
+      <c r="D224" s="53"/>
+      <c r="E224" s="53"/>
+      <c r="F224" s="54"/>
+      <c r="G224" s="53"/>
+      <c r="H224" s="53"/>
+      <c r="I224" s="53"/>
+      <c r="J224" s="54"/>
     </row>
     <row r="225" ht="15.75" customHeight="1">
-      <c r="B225" s="50"/>
-      <c r="C225" s="51"/>
-      <c r="D225" s="51"/>
-      <c r="E225" s="51"/>
-      <c r="F225" s="52"/>
-      <c r="G225" s="51"/>
-      <c r="H225" s="51"/>
-      <c r="I225" s="51"/>
-      <c r="J225" s="52"/>
+      <c r="B225" s="52"/>
+      <c r="C225" s="53"/>
+      <c r="D225" s="53"/>
+      <c r="E225" s="53"/>
+      <c r="F225" s="54"/>
+      <c r="G225" s="53"/>
+      <c r="H225" s="53"/>
+      <c r="I225" s="53"/>
+      <c r="J225" s="54"/>
     </row>
     <row r="226" ht="15.75" customHeight="1">
-      <c r="B226" s="50"/>
-      <c r="C226" s="51"/>
-      <c r="D226" s="51"/>
-      <c r="E226" s="51"/>
-      <c r="F226" s="52"/>
-      <c r="G226" s="51"/>
-      <c r="H226" s="51"/>
-      <c r="I226" s="51"/>
-      <c r="J226" s="52"/>
+      <c r="B226" s="52"/>
+      <c r="C226" s="53"/>
+      <c r="D226" s="53"/>
+      <c r="E226" s="53"/>
+      <c r="F226" s="54"/>
+      <c r="G226" s="53"/>
+      <c r="H226" s="53"/>
+      <c r="I226" s="53"/>
+      <c r="J226" s="54"/>
     </row>
     <row r="227" ht="15.75" customHeight="1">
-      <c r="B227" s="50"/>
-      <c r="C227" s="51"/>
-      <c r="D227" s="51"/>
-      <c r="E227" s="51"/>
-      <c r="F227" s="52"/>
-      <c r="G227" s="51"/>
-      <c r="H227" s="51"/>
-      <c r="I227" s="51"/>
-      <c r="J227" s="52"/>
+      <c r="B227" s="52"/>
+      <c r="C227" s="53"/>
+      <c r="D227" s="53"/>
+      <c r="E227" s="53"/>
+      <c r="F227" s="54"/>
+      <c r="G227" s="53"/>
+      <c r="H227" s="53"/>
+      <c r="I227" s="53"/>
+      <c r="J227" s="54"/>
     </row>
     <row r="228" ht="15.75" customHeight="1">
-      <c r="B228" s="50"/>
-      <c r="C228" s="51"/>
-      <c r="D228" s="51"/>
-      <c r="E228" s="51"/>
-      <c r="F228" s="52"/>
-      <c r="G228" s="51"/>
-      <c r="H228" s="51"/>
-      <c r="I228" s="51"/>
-      <c r="J228" s="52"/>
+      <c r="B228" s="52"/>
+      <c r="C228" s="53"/>
+      <c r="D228" s="53"/>
+      <c r="E228" s="53"/>
+      <c r="F228" s="54"/>
+      <c r="G228" s="53"/>
+      <c r="H228" s="53"/>
+      <c r="I228" s="53"/>
+      <c r="J228" s="54"/>
     </row>
     <row r="229" ht="15.75" customHeight="1">
-      <c r="B229" s="50"/>
-      <c r="C229" s="51"/>
-      <c r="D229" s="51"/>
-      <c r="E229" s="51"/>
-      <c r="F229" s="52"/>
-      <c r="G229" s="51"/>
-      <c r="H229" s="51"/>
-      <c r="I229" s="51"/>
-      <c r="J229" s="52"/>
+      <c r="B229" s="52"/>
+      <c r="C229" s="53"/>
+      <c r="D229" s="53"/>
+      <c r="E229" s="53"/>
+      <c r="F229" s="54"/>
+      <c r="G229" s="53"/>
+      <c r="H229" s="53"/>
+      <c r="I229" s="53"/>
+      <c r="J229" s="54"/>
     </row>
     <row r="230" ht="15.75" customHeight="1">
-      <c r="B230" s="50"/>
-      <c r="C230" s="51"/>
-      <c r="D230" s="51"/>
-      <c r="E230" s="51"/>
-      <c r="F230" s="52"/>
-      <c r="G230" s="51"/>
-      <c r="H230" s="51"/>
-      <c r="I230" s="51"/>
-      <c r="J230" s="52"/>
-    </row>
-    <row r="231" ht="15.75" customHeight="1">
-      <c r="B231" s="50"/>
-      <c r="C231" s="51"/>
-      <c r="D231" s="51"/>
-      <c r="E231" s="51"/>
-      <c r="F231" s="52"/>
-      <c r="G231" s="51"/>
-      <c r="H231" s="51"/>
-      <c r="I231" s="51"/>
-      <c r="J231" s="52"/>
-    </row>
+      <c r="B230" s="52"/>
+      <c r="C230" s="53"/>
+      <c r="D230" s="53"/>
+      <c r="E230" s="53"/>
+      <c r="F230" s="54"/>
+      <c r="G230" s="53"/>
+      <c r="H230" s="53"/>
+      <c r="I230" s="53"/>
+      <c r="J230" s="54"/>
+    </row>
+    <row r="231" ht="15.75" customHeight="1"/>
     <row r="232" ht="15.75" customHeight="1"/>
     <row r="233" ht="15.75" customHeight="1"/>
     <row r="234" ht="15.75" customHeight="1"/>
@@ -4747,9 +4889,8 @@
     <row r="998" ht="15.75" customHeight="1"/>
     <row r="999" ht="15.75" customHeight="1"/>
     <row r="1000" ht="15.75" customHeight="1"/>
-    <row r="1001" ht="15.75" customHeight="1"/>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A3:A8"/>
     <mergeCell ref="A10:A15"/>
     <mergeCell ref="A17:A23"/>
@@ -4757,6 +4898,7 @@
     <mergeCell ref="A25:A30"/>
     <mergeCell ref="A32:A38"/>
     <mergeCell ref="C37:J37"/>
+    <mergeCell ref="A40:A45"/>
   </mergeCells>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
@@ -4781,13 +4923,13 @@
   <sheetData>
     <row r="1" ht="15.75" customHeight="1">
       <c r="A1" s="2" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="B1" s="2" t="s">
-        <v>32</v>
+        <v>35</v>
       </c>
       <c r="C1" s="2" t="s">
-        <v>33</v>
+        <v>36</v>
       </c>
     </row>
     <row r="2" ht="15.75" customHeight="1">
@@ -4795,10 +4937,10 @@
         <v>11</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>34</v>
+        <v>37</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>35</v>
+        <v>38</v>
       </c>
     </row>
     <row r="3" ht="15.75" customHeight="1">
@@ -4806,10 +4948,10 @@
         <v>13</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>36</v>
+        <v>39</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>37</v>
+        <v>40</v>
       </c>
     </row>
     <row r="4" ht="15.75" customHeight="1">
@@ -4817,10 +4959,10 @@
         <v>15</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>39</v>
+        <v>42</v>
       </c>
     </row>
     <row r="5" ht="15.75" customHeight="1">
@@ -4828,10 +4970,10 @@
         <v>16</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>40</v>
+        <v>43</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>44</v>
       </c>
     </row>
     <row r="6" ht="15.75" customHeight="1">
@@ -4839,10 +4981,10 @@
         <v>18</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>42</v>
+        <v>45</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>43</v>
+        <v>46</v>
       </c>
     </row>
     <row r="7" ht="15.75" customHeight="1">
@@ -4850,1084 +4992,1084 @@
         <v>19</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>44</v>
+        <v>47</v>
       </c>
       <c r="C7" s="6" t="s">
-        <v>45</v>
+        <v>48</v>
       </c>
     </row>
     <row r="8" ht="15.75" customHeight="1">
-      <c r="A8" s="50"/>
-      <c r="B8" s="50"/>
-      <c r="C8" s="50"/>
+      <c r="A8" s="52"/>
+      <c r="B8" s="52"/>
+      <c r="C8" s="52"/>
     </row>
     <row r="9" ht="15.75" customHeight="1">
       <c r="A9" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="B9" s="50"/>
-      <c r="C9" s="50"/>
+        <v>49</v>
+      </c>
+      <c r="B9" s="52"/>
+      <c r="C9" s="52"/>
     </row>
     <row r="10" ht="15.75" customHeight="1">
       <c r="A10" s="6" t="s">
-        <v>47</v>
-      </c>
-      <c r="B10" s="50"/>
-      <c r="C10" s="50"/>
+        <v>50</v>
+      </c>
+      <c r="B10" s="52"/>
+      <c r="C10" s="52"/>
     </row>
     <row r="11" ht="15.75" customHeight="1">
       <c r="A11" s="6" t="s">
-        <v>48</v>
-      </c>
-      <c r="B11" s="50"/>
-      <c r="C11" s="50"/>
+        <v>51</v>
+      </c>
+      <c r="B11" s="52"/>
+      <c r="C11" s="52"/>
     </row>
     <row r="12" ht="15.75" customHeight="1">
       <c r="A12" s="6" t="s">
-        <v>49</v>
-      </c>
-      <c r="B12" s="50"/>
-      <c r="C12" s="50"/>
+        <v>52</v>
+      </c>
+      <c r="B12" s="52"/>
+      <c r="C12" s="52"/>
     </row>
     <row r="13" ht="15.75" customHeight="1">
-      <c r="A13" s="50"/>
+      <c r="A13" s="52"/>
       <c r="B13" s="6"/>
-      <c r="C13" s="50"/>
+      <c r="C13" s="52"/>
     </row>
     <row r="14" ht="15.75" customHeight="1">
-      <c r="A14" s="50"/>
-      <c r="B14" s="50"/>
-      <c r="C14" s="50"/>
+      <c r="A14" s="52"/>
+      <c r="B14" s="52"/>
+      <c r="C14" s="52"/>
     </row>
     <row r="15" ht="15.75" customHeight="1">
-      <c r="A15" s="50"/>
-      <c r="B15" s="50"/>
-      <c r="C15" s="50"/>
+      <c r="A15" s="52"/>
+      <c r="B15" s="52"/>
+      <c r="C15" s="52"/>
     </row>
     <row r="16" ht="15.75" customHeight="1">
-      <c r="A16" s="50"/>
-      <c r="B16" s="50"/>
-      <c r="C16" s="50"/>
+      <c r="A16" s="52"/>
+      <c r="B16" s="52"/>
+      <c r="C16" s="52"/>
     </row>
     <row r="17" ht="15.75" customHeight="1">
-      <c r="A17" s="50"/>
-      <c r="B17" s="50"/>
-      <c r="C17" s="50"/>
+      <c r="A17" s="52"/>
+      <c r="B17" s="52"/>
+      <c r="C17" s="52"/>
     </row>
     <row r="18" ht="15.75" customHeight="1">
-      <c r="A18" s="50"/>
-      <c r="B18" s="50"/>
-      <c r="C18" s="50"/>
+      <c r="A18" s="52"/>
+      <c r="B18" s="52"/>
+      <c r="C18" s="52"/>
     </row>
     <row r="19" ht="15.75" customHeight="1">
-      <c r="A19" s="50"/>
-      <c r="B19" s="50"/>
-      <c r="C19" s="50"/>
+      <c r="A19" s="52"/>
+      <c r="B19" s="52"/>
+      <c r="C19" s="52"/>
     </row>
     <row r="20" ht="15.75" customHeight="1">
-      <c r="A20" s="50"/>
-      <c r="B20" s="50"/>
-      <c r="C20" s="50"/>
+      <c r="A20" s="52"/>
+      <c r="B20" s="52"/>
+      <c r="C20" s="52"/>
     </row>
     <row r="21" ht="15.75" customHeight="1">
-      <c r="A21" s="50"/>
-      <c r="B21" s="50"/>
-      <c r="C21" s="50"/>
+      <c r="A21" s="52"/>
+      <c r="B21" s="52"/>
+      <c r="C21" s="52"/>
     </row>
     <row r="22" ht="15.75" customHeight="1">
-      <c r="A22" s="50"/>
-      <c r="B22" s="50"/>
-      <c r="C22" s="50"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
+      <c r="C22" s="52"/>
     </row>
     <row r="23" ht="15.75" customHeight="1">
-      <c r="A23" s="50"/>
-      <c r="B23" s="50"/>
-      <c r="C23" s="50"/>
+      <c r="A23" s="52"/>
+      <c r="B23" s="52"/>
+      <c r="C23" s="52"/>
     </row>
     <row r="24" ht="15.75" customHeight="1">
-      <c r="A24" s="50"/>
-      <c r="B24" s="50"/>
-      <c r="C24" s="50"/>
+      <c r="A24" s="52"/>
+      <c r="B24" s="52"/>
+      <c r="C24" s="52"/>
     </row>
     <row r="25" ht="15.75" customHeight="1">
-      <c r="A25" s="50"/>
-      <c r="B25" s="50"/>
-      <c r="C25" s="50"/>
+      <c r="A25" s="52"/>
+      <c r="B25" s="52"/>
+      <c r="C25" s="52"/>
     </row>
     <row r="26" ht="15.75" customHeight="1">
-      <c r="A26" s="50"/>
-      <c r="B26" s="50"/>
-      <c r="C26" s="50"/>
+      <c r="A26" s="52"/>
+      <c r="B26" s="52"/>
+      <c r="C26" s="52"/>
     </row>
     <row r="27" ht="15.75" customHeight="1">
-      <c r="A27" s="50"/>
-      <c r="B27" s="50"/>
-      <c r="C27" s="50"/>
+      <c r="A27" s="52"/>
+      <c r="B27" s="52"/>
+      <c r="C27" s="52"/>
     </row>
     <row r="28" ht="15.75" customHeight="1">
-      <c r="A28" s="50"/>
-      <c r="B28" s="50"/>
-      <c r="C28" s="50"/>
+      <c r="A28" s="52"/>
+      <c r="B28" s="52"/>
+      <c r="C28" s="52"/>
     </row>
     <row r="29" ht="15.75" customHeight="1">
-      <c r="A29" s="50"/>
-      <c r="B29" s="50"/>
-      <c r="C29" s="50"/>
+      <c r="A29" s="52"/>
+      <c r="B29" s="52"/>
+      <c r="C29" s="52"/>
     </row>
     <row r="30" ht="15.75" customHeight="1">
-      <c r="A30" s="50"/>
-      <c r="B30" s="50"/>
-      <c r="C30" s="50"/>
+      <c r="A30" s="52"/>
+      <c r="B30" s="52"/>
+      <c r="C30" s="52"/>
     </row>
     <row r="31" ht="15.75" customHeight="1">
-      <c r="A31" s="50"/>
-      <c r="B31" s="50"/>
-      <c r="C31" s="50"/>
+      <c r="A31" s="52"/>
+      <c r="B31" s="52"/>
+      <c r="C31" s="52"/>
     </row>
     <row r="32" ht="15.75" customHeight="1">
-      <c r="A32" s="50"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="50"/>
+      <c r="A32" s="52"/>
+      <c r="B32" s="52"/>
+      <c r="C32" s="52"/>
     </row>
     <row r="33" ht="15.75" customHeight="1">
-      <c r="A33" s="50"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="50"/>
+      <c r="A33" s="52"/>
+      <c r="B33" s="52"/>
+      <c r="C33" s="52"/>
     </row>
     <row r="34" ht="15.75" customHeight="1">
-      <c r="A34" s="50"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="50"/>
+      <c r="A34" s="52"/>
+      <c r="B34" s="52"/>
+      <c r="C34" s="52"/>
     </row>
     <row r="35" ht="15.75" customHeight="1">
-      <c r="A35" s="50"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="50"/>
+      <c r="A35" s="52"/>
+      <c r="B35" s="52"/>
+      <c r="C35" s="52"/>
     </row>
     <row r="36" ht="15.75" customHeight="1">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="50"/>
+      <c r="A36" s="52"/>
+      <c r="B36" s="52"/>
+      <c r="C36" s="52"/>
     </row>
     <row r="37" ht="15.75" customHeight="1">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="50"/>
+      <c r="A37" s="52"/>
+      <c r="B37" s="52"/>
+      <c r="C37" s="52"/>
     </row>
     <row r="38" ht="15.75" customHeight="1">
-      <c r="A38" s="50"/>
-      <c r="B38" s="50"/>
-      <c r="C38" s="50"/>
+      <c r="A38" s="52"/>
+      <c r="B38" s="52"/>
+      <c r="C38" s="52"/>
     </row>
     <row r="39" ht="15.75" customHeight="1">
-      <c r="A39" s="50"/>
-      <c r="B39" s="50"/>
-      <c r="C39" s="50"/>
+      <c r="A39" s="52"/>
+      <c r="B39" s="52"/>
+      <c r="C39" s="52"/>
     </row>
     <row r="40" ht="15.75" customHeight="1">
-      <c r="A40" s="50"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="50"/>
+      <c r="A40" s="52"/>
+      <c r="B40" s="52"/>
+      <c r="C40" s="52"/>
     </row>
     <row r="41" ht="15.75" customHeight="1">
-      <c r="A41" s="50"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="50"/>
+      <c r="A41" s="52"/>
+      <c r="B41" s="52"/>
+      <c r="C41" s="52"/>
     </row>
     <row r="42" ht="15.75" customHeight="1">
-      <c r="A42" s="50"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="50"/>
+      <c r="A42" s="52"/>
+      <c r="B42" s="52"/>
+      <c r="C42" s="52"/>
     </row>
     <row r="43" ht="15.75" customHeight="1">
-      <c r="A43" s="50"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="50"/>
+      <c r="A43" s="52"/>
+      <c r="B43" s="52"/>
+      <c r="C43" s="52"/>
     </row>
     <row r="44" ht="15.75" customHeight="1">
-      <c r="A44" s="50"/>
-      <c r="B44" s="50"/>
-      <c r="C44" s="50"/>
+      <c r="A44" s="52"/>
+      <c r="B44" s="52"/>
+      <c r="C44" s="52"/>
     </row>
     <row r="45" ht="15.75" customHeight="1">
-      <c r="A45" s="50"/>
-      <c r="B45" s="50"/>
-      <c r="C45" s="50"/>
+      <c r="A45" s="52"/>
+      <c r="B45" s="52"/>
+      <c r="C45" s="52"/>
     </row>
     <row r="46" ht="15.75" customHeight="1">
-      <c r="A46" s="50"/>
-      <c r="B46" s="50"/>
-      <c r="C46" s="50"/>
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
+      <c r="C46" s="52"/>
     </row>
     <row r="47" ht="15.75" customHeight="1">
-      <c r="A47" s="50"/>
-      <c r="B47" s="50"/>
-      <c r="C47" s="50"/>
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
+      <c r="C47" s="52"/>
     </row>
     <row r="48" ht="15.75" customHeight="1">
-      <c r="A48" s="50"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="50"/>
+      <c r="A48" s="52"/>
+      <c r="B48" s="52"/>
+      <c r="C48" s="52"/>
     </row>
     <row r="49" ht="15.75" customHeight="1">
-      <c r="A49" s="50"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="50"/>
+      <c r="A49" s="52"/>
+      <c r="B49" s="52"/>
+      <c r="C49" s="52"/>
     </row>
     <row r="50" ht="15.75" customHeight="1">
-      <c r="A50" s="50"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="50"/>
+      <c r="A50" s="52"/>
+      <c r="B50" s="52"/>
+      <c r="C50" s="52"/>
     </row>
     <row r="51" ht="15.75" customHeight="1">
-      <c r="A51" s="50"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="50"/>
+      <c r="A51" s="52"/>
+      <c r="B51" s="52"/>
+      <c r="C51" s="52"/>
     </row>
     <row r="52" ht="15.75" customHeight="1">
-      <c r="A52" s="50"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="50"/>
+      <c r="A52" s="52"/>
+      <c r="B52" s="52"/>
+      <c r="C52" s="52"/>
     </row>
     <row r="53" ht="15.75" customHeight="1">
-      <c r="A53" s="50"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="50"/>
+      <c r="A53" s="52"/>
+      <c r="B53" s="52"/>
+      <c r="C53" s="52"/>
     </row>
     <row r="54" ht="15.75" customHeight="1">
-      <c r="A54" s="50"/>
-      <c r="B54" s="50"/>
-      <c r="C54" s="50"/>
+      <c r="A54" s="52"/>
+      <c r="B54" s="52"/>
+      <c r="C54" s="52"/>
     </row>
     <row r="55" ht="15.75" customHeight="1">
-      <c r="A55" s="50"/>
-      <c r="B55" s="50"/>
-      <c r="C55" s="50"/>
+      <c r="A55" s="52"/>
+      <c r="B55" s="52"/>
+      <c r="C55" s="52"/>
     </row>
     <row r="56" ht="15.75" customHeight="1">
-      <c r="A56" s="50"/>
-      <c r="B56" s="50"/>
-      <c r="C56" s="50"/>
+      <c r="A56" s="52"/>
+      <c r="B56" s="52"/>
+      <c r="C56" s="52"/>
     </row>
     <row r="57" ht="15.75" customHeight="1">
-      <c r="A57" s="50"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="50"/>
+      <c r="A57" s="52"/>
+      <c r="B57" s="52"/>
+      <c r="C57" s="52"/>
     </row>
     <row r="58" ht="15.75" customHeight="1">
-      <c r="A58" s="50"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="50"/>
+      <c r="A58" s="52"/>
+      <c r="B58" s="52"/>
+      <c r="C58" s="52"/>
     </row>
     <row r="59" ht="15.75" customHeight="1">
-      <c r="A59" s="50"/>
-      <c r="B59" s="50"/>
-      <c r="C59" s="50"/>
+      <c r="A59" s="52"/>
+      <c r="B59" s="52"/>
+      <c r="C59" s="52"/>
     </row>
     <row r="60" ht="15.75" customHeight="1">
-      <c r="A60" s="50"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="50"/>
+      <c r="A60" s="52"/>
+      <c r="B60" s="52"/>
+      <c r="C60" s="52"/>
     </row>
     <row r="61" ht="15.75" customHeight="1">
-      <c r="A61" s="50"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="50"/>
+      <c r="A61" s="52"/>
+      <c r="B61" s="52"/>
+      <c r="C61" s="52"/>
     </row>
     <row r="62" ht="15.75" customHeight="1">
-      <c r="A62" s="50"/>
-      <c r="B62" s="50"/>
-      <c r="C62" s="50"/>
+      <c r="A62" s="52"/>
+      <c r="B62" s="52"/>
+      <c r="C62" s="52"/>
     </row>
     <row r="63" ht="15.75" customHeight="1">
-      <c r="A63" s="50"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="50"/>
+      <c r="A63" s="52"/>
+      <c r="B63" s="52"/>
+      <c r="C63" s="52"/>
     </row>
     <row r="64" ht="15.75" customHeight="1">
-      <c r="A64" s="50"/>
-      <c r="B64" s="50"/>
-      <c r="C64" s="50"/>
+      <c r="A64" s="52"/>
+      <c r="B64" s="52"/>
+      <c r="C64" s="52"/>
     </row>
     <row r="65" ht="15.75" customHeight="1">
-      <c r="A65" s="50"/>
-      <c r="B65" s="50"/>
-      <c r="C65" s="50"/>
+      <c r="A65" s="52"/>
+      <c r="B65" s="52"/>
+      <c r="C65" s="52"/>
     </row>
     <row r="66" ht="15.75" customHeight="1">
-      <c r="A66" s="50"/>
-      <c r="B66" s="50"/>
-      <c r="C66" s="50"/>
+      <c r="A66" s="52"/>
+      <c r="B66" s="52"/>
+      <c r="C66" s="52"/>
     </row>
     <row r="67" ht="15.75" customHeight="1">
-      <c r="A67" s="50"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="50"/>
+      <c r="A67" s="52"/>
+      <c r="B67" s="52"/>
+      <c r="C67" s="52"/>
     </row>
     <row r="68" ht="15.75" customHeight="1">
-      <c r="A68" s="50"/>
-      <c r="B68" s="50"/>
-      <c r="C68" s="50"/>
+      <c r="A68" s="52"/>
+      <c r="B68" s="52"/>
+      <c r="C68" s="52"/>
     </row>
     <row r="69" ht="15.75" customHeight="1">
-      <c r="A69" s="50"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="50"/>
+      <c r="A69" s="52"/>
+      <c r="B69" s="52"/>
+      <c r="C69" s="52"/>
     </row>
     <row r="70" ht="15.75" customHeight="1">
-      <c r="A70" s="50"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="50"/>
+      <c r="A70" s="52"/>
+      <c r="B70" s="52"/>
+      <c r="C70" s="52"/>
     </row>
     <row r="71" ht="15.75" customHeight="1">
-      <c r="A71" s="50"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="50"/>
+      <c r="A71" s="52"/>
+      <c r="B71" s="52"/>
+      <c r="C71" s="52"/>
     </row>
     <row r="72" ht="15.75" customHeight="1">
-      <c r="A72" s="50"/>
-      <c r="B72" s="50"/>
-      <c r="C72" s="50"/>
+      <c r="A72" s="52"/>
+      <c r="B72" s="52"/>
+      <c r="C72" s="52"/>
     </row>
     <row r="73" ht="15.75" customHeight="1">
-      <c r="A73" s="50"/>
-      <c r="B73" s="50"/>
-      <c r="C73" s="50"/>
+      <c r="A73" s="52"/>
+      <c r="B73" s="52"/>
+      <c r="C73" s="52"/>
     </row>
     <row r="74" ht="15.75" customHeight="1">
-      <c r="A74" s="50"/>
-      <c r="B74" s="50"/>
-      <c r="C74" s="50"/>
+      <c r="A74" s="52"/>
+      <c r="B74" s="52"/>
+      <c r="C74" s="52"/>
     </row>
     <row r="75" ht="15.75" customHeight="1">
-      <c r="A75" s="50"/>
-      <c r="B75" s="50"/>
-      <c r="C75" s="50"/>
+      <c r="A75" s="52"/>
+      <c r="B75" s="52"/>
+      <c r="C75" s="52"/>
     </row>
     <row r="76" ht="15.75" customHeight="1">
-      <c r="A76" s="50"/>
-      <c r="B76" s="50"/>
-      <c r="C76" s="50"/>
+      <c r="A76" s="52"/>
+      <c r="B76" s="52"/>
+      <c r="C76" s="52"/>
     </row>
     <row r="77" ht="15.75" customHeight="1">
-      <c r="A77" s="50"/>
-      <c r="B77" s="50"/>
-      <c r="C77" s="50"/>
+      <c r="A77" s="52"/>
+      <c r="B77" s="52"/>
+      <c r="C77" s="52"/>
     </row>
     <row r="78" ht="15.75" customHeight="1">
-      <c r="A78" s="50"/>
-      <c r="B78" s="50"/>
-      <c r="C78" s="50"/>
+      <c r="A78" s="52"/>
+      <c r="B78" s="52"/>
+      <c r="C78" s="52"/>
     </row>
     <row r="79" ht="15.75" customHeight="1">
-      <c r="A79" s="50"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="50"/>
+      <c r="A79" s="52"/>
+      <c r="B79" s="52"/>
+      <c r="C79" s="52"/>
     </row>
     <row r="80" ht="15.75" customHeight="1">
-      <c r="A80" s="50"/>
-      <c r="B80" s="50"/>
-      <c r="C80" s="50"/>
+      <c r="A80" s="52"/>
+      <c r="B80" s="52"/>
+      <c r="C80" s="52"/>
     </row>
     <row r="81" ht="15.75" customHeight="1">
-      <c r="A81" s="50"/>
-      <c r="B81" s="50"/>
-      <c r="C81" s="50"/>
+      <c r="A81" s="52"/>
+      <c r="B81" s="52"/>
+      <c r="C81" s="52"/>
     </row>
     <row r="82" ht="15.75" customHeight="1">
-      <c r="A82" s="50"/>
-      <c r="B82" s="50"/>
-      <c r="C82" s="50"/>
+      <c r="A82" s="52"/>
+      <c r="B82" s="52"/>
+      <c r="C82" s="52"/>
     </row>
     <row r="83" ht="15.75" customHeight="1">
-      <c r="A83" s="50"/>
-      <c r="B83" s="50"/>
-      <c r="C83" s="50"/>
+      <c r="A83" s="52"/>
+      <c r="B83" s="52"/>
+      <c r="C83" s="52"/>
     </row>
     <row r="84" ht="15.75" customHeight="1">
-      <c r="A84" s="50"/>
-      <c r="B84" s="50"/>
-      <c r="C84" s="50"/>
+      <c r="A84" s="52"/>
+      <c r="B84" s="52"/>
+      <c r="C84" s="52"/>
     </row>
     <row r="85" ht="15.75" customHeight="1">
-      <c r="A85" s="50"/>
-      <c r="B85" s="50"/>
-      <c r="C85" s="50"/>
+      <c r="A85" s="52"/>
+      <c r="B85" s="52"/>
+      <c r="C85" s="52"/>
     </row>
     <row r="86" ht="15.75" customHeight="1">
-      <c r="A86" s="50"/>
-      <c r="B86" s="50"/>
-      <c r="C86" s="50"/>
+      <c r="A86" s="52"/>
+      <c r="B86" s="52"/>
+      <c r="C86" s="52"/>
     </row>
     <row r="87" ht="15.75" customHeight="1">
-      <c r="A87" s="50"/>
-      <c r="B87" s="50"/>
-      <c r="C87" s="50"/>
+      <c r="A87" s="52"/>
+      <c r="B87" s="52"/>
+      <c r="C87" s="52"/>
     </row>
     <row r="88" ht="15.75" customHeight="1">
-      <c r="A88" s="50"/>
-      <c r="B88" s="50"/>
-      <c r="C88" s="50"/>
+      <c r="A88" s="52"/>
+      <c r="B88" s="52"/>
+      <c r="C88" s="52"/>
     </row>
     <row r="89" ht="15.75" customHeight="1">
-      <c r="A89" s="50"/>
-      <c r="B89" s="50"/>
-      <c r="C89" s="50"/>
+      <c r="A89" s="52"/>
+      <c r="B89" s="52"/>
+      <c r="C89" s="52"/>
     </row>
     <row r="90" ht="15.75" customHeight="1">
-      <c r="A90" s="50"/>
-      <c r="B90" s="50"/>
-      <c r="C90" s="50"/>
+      <c r="A90" s="52"/>
+      <c r="B90" s="52"/>
+      <c r="C90" s="52"/>
     </row>
     <row r="91" ht="15.75" customHeight="1">
-      <c r="A91" s="50"/>
-      <c r="B91" s="50"/>
-      <c r="C91" s="50"/>
+      <c r="A91" s="52"/>
+      <c r="B91" s="52"/>
+      <c r="C91" s="52"/>
     </row>
     <row r="92" ht="15.75" customHeight="1">
-      <c r="A92" s="50"/>
-      <c r="B92" s="50"/>
-      <c r="C92" s="50"/>
+      <c r="A92" s="52"/>
+      <c r="B92" s="52"/>
+      <c r="C92" s="52"/>
     </row>
     <row r="93" ht="15.75" customHeight="1">
-      <c r="A93" s="50"/>
-      <c r="B93" s="50"/>
-      <c r="C93" s="50"/>
+      <c r="A93" s="52"/>
+      <c r="B93" s="52"/>
+      <c r="C93" s="52"/>
     </row>
     <row r="94" ht="15.75" customHeight="1">
-      <c r="A94" s="50"/>
-      <c r="B94" s="50"/>
-      <c r="C94" s="50"/>
+      <c r="A94" s="52"/>
+      <c r="B94" s="52"/>
+      <c r="C94" s="52"/>
     </row>
     <row r="95" ht="15.75" customHeight="1">
-      <c r="A95" s="50"/>
-      <c r="B95" s="50"/>
-      <c r="C95" s="50"/>
+      <c r="A95" s="52"/>
+      <c r="B95" s="52"/>
+      <c r="C95" s="52"/>
     </row>
     <row r="96" ht="15.75" customHeight="1">
-      <c r="A96" s="50"/>
-      <c r="B96" s="50"/>
-      <c r="C96" s="50"/>
+      <c r="A96" s="52"/>
+      <c r="B96" s="52"/>
+      <c r="C96" s="52"/>
     </row>
     <row r="97" ht="15.75" customHeight="1">
-      <c r="A97" s="50"/>
-      <c r="B97" s="50"/>
-      <c r="C97" s="50"/>
+      <c r="A97" s="52"/>
+      <c r="B97" s="52"/>
+      <c r="C97" s="52"/>
     </row>
     <row r="98" ht="15.75" customHeight="1">
-      <c r="A98" s="50"/>
-      <c r="B98" s="50"/>
-      <c r="C98" s="50"/>
+      <c r="A98" s="52"/>
+      <c r="B98" s="52"/>
+      <c r="C98" s="52"/>
     </row>
     <row r="99" ht="15.75" customHeight="1">
-      <c r="A99" s="50"/>
-      <c r="B99" s="50"/>
-      <c r="C99" s="50"/>
+      <c r="A99" s="52"/>
+      <c r="B99" s="52"/>
+      <c r="C99" s="52"/>
     </row>
     <row r="100" ht="15.75" customHeight="1">
-      <c r="A100" s="50"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="50"/>
+      <c r="A100" s="52"/>
+      <c r="B100" s="52"/>
+      <c r="C100" s="52"/>
     </row>
     <row r="101" ht="15.75" customHeight="1">
-      <c r="A101" s="50"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="50"/>
+      <c r="A101" s="52"/>
+      <c r="B101" s="52"/>
+      <c r="C101" s="52"/>
     </row>
     <row r="102" ht="15.75" customHeight="1">
-      <c r="A102" s="50"/>
-      <c r="B102" s="50"/>
-      <c r="C102" s="50"/>
+      <c r="A102" s="52"/>
+      <c r="B102" s="52"/>
+      <c r="C102" s="52"/>
     </row>
     <row r="103" ht="15.75" customHeight="1">
-      <c r="A103" s="50"/>
-      <c r="B103" s="50"/>
-      <c r="C103" s="50"/>
+      <c r="A103" s="52"/>
+      <c r="B103" s="52"/>
+      <c r="C103" s="52"/>
     </row>
     <row r="104" ht="15.75" customHeight="1">
-      <c r="A104" s="50"/>
-      <c r="B104" s="50"/>
-      <c r="C104" s="50"/>
+      <c r="A104" s="52"/>
+      <c r="B104" s="52"/>
+      <c r="C104" s="52"/>
     </row>
     <row r="105" ht="15.75" customHeight="1">
-      <c r="A105" s="50"/>
-      <c r="B105" s="50"/>
-      <c r="C105" s="50"/>
+      <c r="A105" s="52"/>
+      <c r="B105" s="52"/>
+      <c r="C105" s="52"/>
     </row>
     <row r="106" ht="15.75" customHeight="1">
-      <c r="A106" s="50"/>
-      <c r="B106" s="50"/>
-      <c r="C106" s="50"/>
+      <c r="A106" s="52"/>
+      <c r="B106" s="52"/>
+      <c r="C106" s="52"/>
     </row>
     <row r="107" ht="15.75" customHeight="1">
-      <c r="A107" s="50"/>
-      <c r="B107" s="50"/>
-      <c r="C107" s="50"/>
+      <c r="A107" s="52"/>
+      <c r="B107" s="52"/>
+      <c r="C107" s="52"/>
     </row>
     <row r="108" ht="15.75" customHeight="1">
-      <c r="A108" s="50"/>
-      <c r="B108" s="50"/>
-      <c r="C108" s="50"/>
+      <c r="A108" s="52"/>
+      <c r="B108" s="52"/>
+      <c r="C108" s="52"/>
     </row>
     <row r="109" ht="15.75" customHeight="1">
-      <c r="A109" s="50"/>
-      <c r="B109" s="50"/>
-      <c r="C109" s="50"/>
+      <c r="A109" s="52"/>
+      <c r="B109" s="52"/>
+      <c r="C109" s="52"/>
     </row>
     <row r="110" ht="15.75" customHeight="1">
-      <c r="A110" s="50"/>
-      <c r="B110" s="50"/>
-      <c r="C110" s="50"/>
+      <c r="A110" s="52"/>
+      <c r="B110" s="52"/>
+      <c r="C110" s="52"/>
     </row>
     <row r="111" ht="15.75" customHeight="1">
-      <c r="A111" s="50"/>
-      <c r="B111" s="50"/>
-      <c r="C111" s="50"/>
+      <c r="A111" s="52"/>
+      <c r="B111" s="52"/>
+      <c r="C111" s="52"/>
     </row>
     <row r="112" ht="15.75" customHeight="1">
-      <c r="A112" s="50"/>
-      <c r="B112" s="50"/>
-      <c r="C112" s="50"/>
+      <c r="A112" s="52"/>
+      <c r="B112" s="52"/>
+      <c r="C112" s="52"/>
     </row>
     <row r="113" ht="15.75" customHeight="1">
-      <c r="A113" s="50"/>
-      <c r="B113" s="50"/>
-      <c r="C113" s="50"/>
+      <c r="A113" s="52"/>
+      <c r="B113" s="52"/>
+      <c r="C113" s="52"/>
     </row>
     <row r="114" ht="15.75" customHeight="1">
-      <c r="A114" s="50"/>
-      <c r="B114" s="50"/>
-      <c r="C114" s="50"/>
+      <c r="A114" s="52"/>
+      <c r="B114" s="52"/>
+      <c r="C114" s="52"/>
     </row>
     <row r="115" ht="15.75" customHeight="1">
-      <c r="A115" s="50"/>
-      <c r="B115" s="50"/>
-      <c r="C115" s="50"/>
+      <c r="A115" s="52"/>
+      <c r="B115" s="52"/>
+      <c r="C115" s="52"/>
     </row>
     <row r="116" ht="15.75" customHeight="1">
-      <c r="A116" s="50"/>
-      <c r="B116" s="50"/>
-      <c r="C116" s="50"/>
+      <c r="A116" s="52"/>
+      <c r="B116" s="52"/>
+      <c r="C116" s="52"/>
     </row>
     <row r="117" ht="15.75" customHeight="1">
-      <c r="A117" s="50"/>
-      <c r="B117" s="50"/>
-      <c r="C117" s="50"/>
+      <c r="A117" s="52"/>
+      <c r="B117" s="52"/>
+      <c r="C117" s="52"/>
     </row>
     <row r="118" ht="15.75" customHeight="1">
-      <c r="A118" s="50"/>
-      <c r="B118" s="50"/>
-      <c r="C118" s="50"/>
+      <c r="A118" s="52"/>
+      <c r="B118" s="52"/>
+      <c r="C118" s="52"/>
     </row>
     <row r="119" ht="15.75" customHeight="1">
-      <c r="A119" s="50"/>
-      <c r="B119" s="50"/>
-      <c r="C119" s="50"/>
+      <c r="A119" s="52"/>
+      <c r="B119" s="52"/>
+      <c r="C119" s="52"/>
     </row>
     <row r="120" ht="15.75" customHeight="1">
-      <c r="A120" s="50"/>
-      <c r="B120" s="50"/>
-      <c r="C120" s="50"/>
+      <c r="A120" s="52"/>
+      <c r="B120" s="52"/>
+      <c r="C120" s="52"/>
     </row>
     <row r="121" ht="15.75" customHeight="1">
-      <c r="A121" s="50"/>
-      <c r="B121" s="50"/>
-      <c r="C121" s="50"/>
+      <c r="A121" s="52"/>
+      <c r="B121" s="52"/>
+      <c r="C121" s="52"/>
     </row>
     <row r="122" ht="15.75" customHeight="1">
-      <c r="A122" s="50"/>
-      <c r="B122" s="50"/>
-      <c r="C122" s="50"/>
+      <c r="A122" s="52"/>
+      <c r="B122" s="52"/>
+      <c r="C122" s="52"/>
     </row>
     <row r="123" ht="15.75" customHeight="1">
-      <c r="A123" s="50"/>
-      <c r="B123" s="50"/>
-      <c r="C123" s="50"/>
+      <c r="A123" s="52"/>
+      <c r="B123" s="52"/>
+      <c r="C123" s="52"/>
     </row>
     <row r="124" ht="15.75" customHeight="1">
-      <c r="A124" s="50"/>
-      <c r="B124" s="50"/>
-      <c r="C124" s="50"/>
+      <c r="A124" s="52"/>
+      <c r="B124" s="52"/>
+      <c r="C124" s="52"/>
     </row>
     <row r="125" ht="15.75" customHeight="1">
-      <c r="A125" s="50"/>
-      <c r="B125" s="50"/>
-      <c r="C125" s="50"/>
+      <c r="A125" s="52"/>
+      <c r="B125" s="52"/>
+      <c r="C125" s="52"/>
     </row>
     <row r="126" ht="15.75" customHeight="1">
-      <c r="A126" s="50"/>
-      <c r="B126" s="50"/>
-      <c r="C126" s="50"/>
+      <c r="A126" s="52"/>
+      <c r="B126" s="52"/>
+      <c r="C126" s="52"/>
     </row>
     <row r="127" ht="15.75" customHeight="1">
-      <c r="A127" s="50"/>
-      <c r="B127" s="50"/>
-      <c r="C127" s="50"/>
+      <c r="A127" s="52"/>
+      <c r="B127" s="52"/>
+      <c r="C127" s="52"/>
     </row>
     <row r="128" ht="15.75" customHeight="1">
-      <c r="A128" s="50"/>
-      <c r="B128" s="50"/>
-      <c r="C128" s="50"/>
+      <c r="A128" s="52"/>
+      <c r="B128" s="52"/>
+      <c r="C128" s="52"/>
     </row>
     <row r="129" ht="15.75" customHeight="1">
-      <c r="A129" s="50"/>
-      <c r="B129" s="50"/>
-      <c r="C129" s="50"/>
+      <c r="A129" s="52"/>
+      <c r="B129" s="52"/>
+      <c r="C129" s="52"/>
     </row>
     <row r="130" ht="15.75" customHeight="1">
-      <c r="A130" s="50"/>
-      <c r="B130" s="50"/>
-      <c r="C130" s="50"/>
+      <c r="A130" s="52"/>
+      <c r="B130" s="52"/>
+      <c r="C130" s="52"/>
     </row>
     <row r="131" ht="15.75" customHeight="1">
-      <c r="A131" s="50"/>
-      <c r="B131" s="50"/>
-      <c r="C131" s="50"/>
+      <c r="A131" s="52"/>
+      <c r="B131" s="52"/>
+      <c r="C131" s="52"/>
     </row>
     <row r="132" ht="15.75" customHeight="1">
-      <c r="A132" s="50"/>
-      <c r="B132" s="50"/>
-      <c r="C132" s="50"/>
+      <c r="A132" s="52"/>
+      <c r="B132" s="52"/>
+      <c r="C132" s="52"/>
     </row>
     <row r="133" ht="15.75" customHeight="1">
-      <c r="A133" s="50"/>
-      <c r="B133" s="50"/>
-      <c r="C133" s="50"/>
+      <c r="A133" s="52"/>
+      <c r="B133" s="52"/>
+      <c r="C133" s="52"/>
     </row>
     <row r="134" ht="15.75" customHeight="1">
-      <c r="A134" s="50"/>
-      <c r="B134" s="50"/>
-      <c r="C134" s="50"/>
+      <c r="A134" s="52"/>
+      <c r="B134" s="52"/>
+      <c r="C134" s="52"/>
     </row>
     <row r="135" ht="15.75" customHeight="1">
-      <c r="A135" s="50"/>
-      <c r="B135" s="50"/>
-      <c r="C135" s="50"/>
+      <c r="A135" s="52"/>
+      <c r="B135" s="52"/>
+      <c r="C135" s="52"/>
     </row>
     <row r="136" ht="15.75" customHeight="1">
-      <c r="A136" s="50"/>
-      <c r="B136" s="50"/>
-      <c r="C136" s="50"/>
+      <c r="A136" s="52"/>
+      <c r="B136" s="52"/>
+      <c r="C136" s="52"/>
     </row>
     <row r="137" ht="15.75" customHeight="1">
-      <c r="A137" s="50"/>
-      <c r="B137" s="50"/>
-      <c r="C137" s="50"/>
+      <c r="A137" s="52"/>
+      <c r="B137" s="52"/>
+      <c r="C137" s="52"/>
     </row>
     <row r="138" ht="15.75" customHeight="1">
-      <c r="A138" s="50"/>
-      <c r="B138" s="50"/>
-      <c r="C138" s="50"/>
+      <c r="A138" s="52"/>
+      <c r="B138" s="52"/>
+      <c r="C138" s="52"/>
     </row>
     <row r="139" ht="15.75" customHeight="1">
-      <c r="A139" s="50"/>
-      <c r="B139" s="50"/>
-      <c r="C139" s="50"/>
+      <c r="A139" s="52"/>
+      <c r="B139" s="52"/>
+      <c r="C139" s="52"/>
     </row>
     <row r="140" ht="15.75" customHeight="1">
-      <c r="A140" s="50"/>
-      <c r="B140" s="50"/>
-      <c r="C140" s="50"/>
+      <c r="A140" s="52"/>
+      <c r="B140" s="52"/>
+      <c r="C140" s="52"/>
     </row>
     <row r="141" ht="15.75" customHeight="1">
-      <c r="A141" s="50"/>
-      <c r="B141" s="50"/>
-      <c r="C141" s="50"/>
+      <c r="A141" s="52"/>
+      <c r="B141" s="52"/>
+      <c r="C141" s="52"/>
     </row>
     <row r="142" ht="15.75" customHeight="1">
-      <c r="A142" s="50"/>
-      <c r="B142" s="50"/>
-      <c r="C142" s="50"/>
+      <c r="A142" s="52"/>
+      <c r="B142" s="52"/>
+      <c r="C142" s="52"/>
     </row>
     <row r="143" ht="15.75" customHeight="1">
-      <c r="A143" s="50"/>
-      <c r="B143" s="50"/>
-      <c r="C143" s="50"/>
+      <c r="A143" s="52"/>
+      <c r="B143" s="52"/>
+      <c r="C143" s="52"/>
     </row>
     <row r="144" ht="15.75" customHeight="1">
-      <c r="A144" s="50"/>
-      <c r="B144" s="50"/>
-      <c r="C144" s="50"/>
+      <c r="A144" s="52"/>
+      <c r="B144" s="52"/>
+      <c r="C144" s="52"/>
     </row>
     <row r="145" ht="15.75" customHeight="1">
-      <c r="A145" s="50"/>
-      <c r="B145" s="50"/>
-      <c r="C145" s="50"/>
+      <c r="A145" s="52"/>
+      <c r="B145" s="52"/>
+      <c r="C145" s="52"/>
     </row>
     <row r="146" ht="15.75" customHeight="1">
-      <c r="A146" s="50"/>
-      <c r="B146" s="50"/>
-      <c r="C146" s="50"/>
+      <c r="A146" s="52"/>
+      <c r="B146" s="52"/>
+      <c r="C146" s="52"/>
     </row>
     <row r="147" ht="15.75" customHeight="1">
-      <c r="A147" s="50"/>
-      <c r="B147" s="50"/>
-      <c r="C147" s="50"/>
+      <c r="A147" s="52"/>
+      <c r="B147" s="52"/>
+      <c r="C147" s="52"/>
     </row>
     <row r="148" ht="15.75" customHeight="1">
-      <c r="A148" s="50"/>
-      <c r="B148" s="50"/>
-      <c r="C148" s="50"/>
+      <c r="A148" s="52"/>
+      <c r="B148" s="52"/>
+      <c r="C148" s="52"/>
     </row>
     <row r="149" ht="15.75" customHeight="1">
-      <c r="A149" s="50"/>
-      <c r="B149" s="50"/>
-      <c r="C149" s="50"/>
+      <c r="A149" s="52"/>
+      <c r="B149" s="52"/>
+      <c r="C149" s="52"/>
     </row>
     <row r="150" ht="15.75" customHeight="1">
-      <c r="A150" s="50"/>
-      <c r="B150" s="50"/>
-      <c r="C150" s="50"/>
+      <c r="A150" s="52"/>
+      <c r="B150" s="52"/>
+      <c r="C150" s="52"/>
     </row>
     <row r="151" ht="15.75" customHeight="1">
-      <c r="A151" s="50"/>
-      <c r="B151" s="50"/>
-      <c r="C151" s="50"/>
+      <c r="A151" s="52"/>
+      <c r="B151" s="52"/>
+      <c r="C151" s="52"/>
     </row>
     <row r="152" ht="15.75" customHeight="1">
-      <c r="A152" s="50"/>
-      <c r="B152" s="50"/>
-      <c r="C152" s="50"/>
+      <c r="A152" s="52"/>
+      <c r="B152" s="52"/>
+      <c r="C152" s="52"/>
     </row>
     <row r="153" ht="15.75" customHeight="1">
-      <c r="A153" s="50"/>
-      <c r="B153" s="50"/>
-      <c r="C153" s="50"/>
+      <c r="A153" s="52"/>
+      <c r="B153" s="52"/>
+      <c r="C153" s="52"/>
     </row>
     <row r="154" ht="15.75" customHeight="1">
-      <c r="A154" s="50"/>
-      <c r="B154" s="50"/>
-      <c r="C154" s="50"/>
+      <c r="A154" s="52"/>
+      <c r="B154" s="52"/>
+      <c r="C154" s="52"/>
     </row>
     <row r="155" ht="15.75" customHeight="1">
-      <c r="A155" s="50"/>
-      <c r="B155" s="50"/>
-      <c r="C155" s="50"/>
+      <c r="A155" s="52"/>
+      <c r="B155" s="52"/>
+      <c r="C155" s="52"/>
     </row>
     <row r="156" ht="15.75" customHeight="1">
-      <c r="A156" s="50"/>
-      <c r="B156" s="50"/>
-      <c r="C156" s="50"/>
+      <c r="A156" s="52"/>
+      <c r="B156" s="52"/>
+      <c r="C156" s="52"/>
     </row>
     <row r="157" ht="15.75" customHeight="1">
-      <c r="A157" s="50"/>
-      <c r="B157" s="50"/>
-      <c r="C157" s="50"/>
+      <c r="A157" s="52"/>
+      <c r="B157" s="52"/>
+      <c r="C157" s="52"/>
     </row>
     <row r="158" ht="15.75" customHeight="1">
-      <c r="A158" s="50"/>
-      <c r="B158" s="50"/>
-      <c r="C158" s="50"/>
+      <c r="A158" s="52"/>
+      <c r="B158" s="52"/>
+      <c r="C158" s="52"/>
     </row>
     <row r="159" ht="15.75" customHeight="1">
-      <c r="A159" s="50"/>
-      <c r="B159" s="50"/>
-      <c r="C159" s="50"/>
+      <c r="A159" s="52"/>
+      <c r="B159" s="52"/>
+      <c r="C159" s="52"/>
     </row>
     <row r="160" ht="15.75" customHeight="1">
-      <c r="A160" s="50"/>
-      <c r="B160" s="50"/>
-      <c r="C160" s="50"/>
+      <c r="A160" s="52"/>
+      <c r="B160" s="52"/>
+      <c r="C160" s="52"/>
     </row>
     <row r="161" ht="15.75" customHeight="1">
-      <c r="A161" s="50"/>
-      <c r="B161" s="50"/>
-      <c r="C161" s="50"/>
+      <c r="A161" s="52"/>
+      <c r="B161" s="52"/>
+      <c r="C161" s="52"/>
     </row>
     <row r="162" ht="15.75" customHeight="1">
-      <c r="A162" s="50"/>
-      <c r="B162" s="50"/>
-      <c r="C162" s="50"/>
+      <c r="A162" s="52"/>
+      <c r="B162" s="52"/>
+      <c r="C162" s="52"/>
     </row>
     <row r="163" ht="15.75" customHeight="1">
-      <c r="A163" s="50"/>
-      <c r="B163" s="50"/>
-      <c r="C163" s="50"/>
+      <c r="A163" s="52"/>
+      <c r="B163" s="52"/>
+      <c r="C163" s="52"/>
     </row>
     <row r="164" ht="15.75" customHeight="1">
-      <c r="A164" s="50"/>
-      <c r="B164" s="50"/>
-      <c r="C164" s="50"/>
+      <c r="A164" s="52"/>
+      <c r="B164" s="52"/>
+      <c r="C164" s="52"/>
     </row>
     <row r="165" ht="15.75" customHeight="1">
-      <c r="A165" s="50"/>
-      <c r="B165" s="50"/>
-      <c r="C165" s="50"/>
+      <c r="A165" s="52"/>
+      <c r="B165" s="52"/>
+      <c r="C165" s="52"/>
     </row>
     <row r="166" ht="15.75" customHeight="1">
-      <c r="A166" s="50"/>
-      <c r="B166" s="50"/>
-      <c r="C166" s="50"/>
+      <c r="A166" s="52"/>
+      <c r="B166" s="52"/>
+      <c r="C166" s="52"/>
     </row>
     <row r="167" ht="15.75" customHeight="1">
-      <c r="A167" s="50"/>
-      <c r="B167" s="50"/>
-      <c r="C167" s="50"/>
+      <c r="A167" s="52"/>
+      <c r="B167" s="52"/>
+      <c r="C167" s="52"/>
     </row>
     <row r="168" ht="15.75" customHeight="1">
-      <c r="A168" s="50"/>
-      <c r="B168" s="50"/>
-      <c r="C168" s="50"/>
+      <c r="A168" s="52"/>
+      <c r="B168" s="52"/>
+      <c r="C168" s="52"/>
     </row>
     <row r="169" ht="15.75" customHeight="1">
-      <c r="A169" s="50"/>
-      <c r="B169" s="50"/>
-      <c r="C169" s="50"/>
+      <c r="A169" s="52"/>
+      <c r="B169" s="52"/>
+      <c r="C169" s="52"/>
     </row>
     <row r="170" ht="15.75" customHeight="1">
-      <c r="A170" s="50"/>
-      <c r="B170" s="50"/>
-      <c r="C170" s="50"/>
+      <c r="A170" s="52"/>
+      <c r="B170" s="52"/>
+      <c r="C170" s="52"/>
     </row>
     <row r="171" ht="15.75" customHeight="1">
-      <c r="A171" s="50"/>
-      <c r="B171" s="50"/>
-      <c r="C171" s="50"/>
+      <c r="A171" s="52"/>
+      <c r="B171" s="52"/>
+      <c r="C171" s="52"/>
     </row>
     <row r="172" ht="15.75" customHeight="1">
-      <c r="A172" s="50"/>
-      <c r="B172" s="50"/>
-      <c r="C172" s="50"/>
+      <c r="A172" s="52"/>
+      <c r="B172" s="52"/>
+      <c r="C172" s="52"/>
     </row>
     <row r="173" ht="15.75" customHeight="1">
-      <c r="A173" s="50"/>
-      <c r="B173" s="50"/>
-      <c r="C173" s="50"/>
+      <c r="A173" s="52"/>
+      <c r="B173" s="52"/>
+      <c r="C173" s="52"/>
     </row>
     <row r="174" ht="15.75" customHeight="1">
-      <c r="A174" s="50"/>
-      <c r="B174" s="50"/>
-      <c r="C174" s="50"/>
+      <c r="A174" s="52"/>
+      <c r="B174" s="52"/>
+      <c r="C174" s="52"/>
     </row>
     <row r="175" ht="15.75" customHeight="1">
-      <c r="A175" s="50"/>
-      <c r="B175" s="50"/>
-      <c r="C175" s="50"/>
+      <c r="A175" s="52"/>
+      <c r="B175" s="52"/>
+      <c r="C175" s="52"/>
     </row>
     <row r="176" ht="15.75" customHeight="1">
-      <c r="A176" s="50"/>
-      <c r="B176" s="50"/>
-      <c r="C176" s="50"/>
+      <c r="A176" s="52"/>
+      <c r="B176" s="52"/>
+      <c r="C176" s="52"/>
     </row>
     <row r="177" ht="15.75" customHeight="1">
-      <c r="A177" s="50"/>
-      <c r="B177" s="50"/>
-      <c r="C177" s="50"/>
+      <c r="A177" s="52"/>
+      <c r="B177" s="52"/>
+      <c r="C177" s="52"/>
     </row>
     <row r="178" ht="15.75" customHeight="1">
-      <c r="A178" s="50"/>
-      <c r="B178" s="50"/>
-      <c r="C178" s="50"/>
+      <c r="A178" s="52"/>
+      <c r="B178" s="52"/>
+      <c r="C178" s="52"/>
     </row>
     <row r="179" ht="15.75" customHeight="1">
-      <c r="A179" s="50"/>
-      <c r="B179" s="50"/>
-      <c r="C179" s="50"/>
+      <c r="A179" s="52"/>
+      <c r="B179" s="52"/>
+      <c r="C179" s="52"/>
     </row>
     <row r="180" ht="15.75" customHeight="1">
-      <c r="A180" s="50"/>
-      <c r="B180" s="50"/>
-      <c r="C180" s="50"/>
+      <c r="A180" s="52"/>
+      <c r="B180" s="52"/>
+      <c r="C180" s="52"/>
     </row>
     <row r="181" ht="15.75" customHeight="1">
-      <c r="A181" s="50"/>
-      <c r="B181" s="50"/>
-      <c r="C181" s="50"/>
+      <c r="A181" s="52"/>
+      <c r="B181" s="52"/>
+      <c r="C181" s="52"/>
     </row>
     <row r="182" ht="15.75" customHeight="1">
-      <c r="A182" s="50"/>
-      <c r="B182" s="50"/>
-      <c r="C182" s="50"/>
+      <c r="A182" s="52"/>
+      <c r="B182" s="52"/>
+      <c r="C182" s="52"/>
     </row>
     <row r="183" ht="15.75" customHeight="1">
-      <c r="A183" s="50"/>
-      <c r="B183" s="50"/>
-      <c r="C183" s="50"/>
+      <c r="A183" s="52"/>
+      <c r="B183" s="52"/>
+      <c r="C183" s="52"/>
     </row>
     <row r="184" ht="15.75" customHeight="1">
-      <c r="A184" s="50"/>
-      <c r="B184" s="50"/>
-      <c r="C184" s="50"/>
+      <c r="A184" s="52"/>
+      <c r="B184" s="52"/>
+      <c r="C184" s="52"/>
     </row>
     <row r="185" ht="15.75" customHeight="1">
-      <c r="A185" s="50"/>
-      <c r="B185" s="50"/>
-      <c r="C185" s="50"/>
+      <c r="A185" s="52"/>
+      <c r="B185" s="52"/>
+      <c r="C185" s="52"/>
     </row>
     <row r="186" ht="15.75" customHeight="1">
-      <c r="A186" s="50"/>
-      <c r="B186" s="50"/>
-      <c r="C186" s="50"/>
+      <c r="A186" s="52"/>
+      <c r="B186" s="52"/>
+      <c r="C186" s="52"/>
     </row>
     <row r="187" ht="15.75" customHeight="1">
-      <c r="A187" s="50"/>
-      <c r="B187" s="50"/>
-      <c r="C187" s="50"/>
+      <c r="A187" s="52"/>
+      <c r="B187" s="52"/>
+      <c r="C187" s="52"/>
     </row>
     <row r="188" ht="15.75" customHeight="1">
-      <c r="A188" s="50"/>
-      <c r="B188" s="50"/>
-      <c r="C188" s="50"/>
+      <c r="A188" s="52"/>
+      <c r="B188" s="52"/>
+      <c r="C188" s="52"/>
     </row>
     <row r="189" ht="15.75" customHeight="1">
-      <c r="A189" s="50"/>
-      <c r="B189" s="50"/>
-      <c r="C189" s="50"/>
+      <c r="A189" s="52"/>
+      <c r="B189" s="52"/>
+      <c r="C189" s="52"/>
     </row>
     <row r="190" ht="15.75" customHeight="1">
-      <c r="A190" s="50"/>
-      <c r="B190" s="50"/>
-      <c r="C190" s="50"/>
+      <c r="A190" s="52"/>
+      <c r="B190" s="52"/>
+      <c r="C190" s="52"/>
     </row>
     <row r="191" ht="15.75" customHeight="1">
-      <c r="A191" s="50"/>
-      <c r="B191" s="50"/>
-      <c r="C191" s="50"/>
+      <c r="A191" s="52"/>
+      <c r="B191" s="52"/>
+      <c r="C191" s="52"/>
     </row>
     <row r="192" ht="15.75" customHeight="1">
-      <c r="A192" s="50"/>
-      <c r="B192" s="50"/>
-      <c r="C192" s="50"/>
+      <c r="A192" s="52"/>
+      <c r="B192" s="52"/>
+      <c r="C192" s="52"/>
     </row>
     <row r="193" ht="15.75" customHeight="1">
-      <c r="A193" s="50"/>
-      <c r="B193" s="50"/>
-      <c r="C193" s="50"/>
+      <c r="A193" s="52"/>
+      <c r="B193" s="52"/>
+      <c r="C193" s="52"/>
     </row>
     <row r="194" ht="15.75" customHeight="1">
-      <c r="A194" s="50"/>
-      <c r="B194" s="50"/>
-      <c r="C194" s="50"/>
+      <c r="A194" s="52"/>
+      <c r="B194" s="52"/>
+      <c r="C194" s="52"/>
     </row>
     <row r="195" ht="15.75" customHeight="1">
-      <c r="A195" s="50"/>
-      <c r="B195" s="50"/>
-      <c r="C195" s="50"/>
+      <c r="A195" s="52"/>
+      <c r="B195" s="52"/>
+      <c r="C195" s="52"/>
     </row>
     <row r="196" ht="15.75" customHeight="1">
-      <c r="A196" s="50"/>
-      <c r="B196" s="50"/>
-      <c r="C196" s="50"/>
+      <c r="A196" s="52"/>
+      <c r="B196" s="52"/>
+      <c r="C196" s="52"/>
     </row>
     <row r="197" ht="15.75" customHeight="1">
-      <c r="A197" s="50"/>
-      <c r="B197" s="50"/>
-      <c r="C197" s="50"/>
+      <c r="A197" s="52"/>
+      <c r="B197" s="52"/>
+      <c r="C197" s="52"/>
     </row>
     <row r="198" ht="15.75" customHeight="1">
-      <c r="A198" s="50"/>
-      <c r="B198" s="50"/>
-      <c r="C198" s="50"/>
+      <c r="A198" s="52"/>
+      <c r="B198" s="52"/>
+      <c r="C198" s="52"/>
     </row>
     <row r="199" ht="15.75" customHeight="1">
-      <c r="A199" s="50"/>
-      <c r="B199" s="50"/>
-      <c r="C199" s="50"/>
+      <c r="A199" s="52"/>
+      <c r="B199" s="52"/>
+      <c r="C199" s="52"/>
     </row>
     <row r="200" ht="15.75" customHeight="1">
-      <c r="A200" s="50"/>
-      <c r="B200" s="50"/>
-      <c r="C200" s="50"/>
+      <c r="A200" s="52"/>
+      <c r="B200" s="52"/>
+      <c r="C200" s="52"/>
     </row>
     <row r="201" ht="15.75" customHeight="1">
-      <c r="A201" s="50"/>
-      <c r="B201" s="50"/>
-      <c r="C201" s="50"/>
+      <c r="A201" s="52"/>
+      <c r="B201" s="52"/>
+      <c r="C201" s="52"/>
     </row>
     <row r="202" ht="15.75" customHeight="1">
-      <c r="A202" s="50"/>
-      <c r="B202" s="50"/>
-      <c r="C202" s="50"/>
+      <c r="A202" s="52"/>
+      <c r="B202" s="52"/>
+      <c r="C202" s="52"/>
     </row>
     <row r="203" ht="15.75" customHeight="1">
-      <c r="A203" s="50"/>
-      <c r="B203" s="50"/>
-      <c r="C203" s="50"/>
+      <c r="A203" s="52"/>
+      <c r="B203" s="52"/>
+      <c r="C203" s="52"/>
     </row>
     <row r="204" ht="15.75" customHeight="1">
-      <c r="A204" s="50"/>
-      <c r="B204" s="50"/>
-      <c r="C204" s="50"/>
+      <c r="A204" s="52"/>
+      <c r="B204" s="52"/>
+      <c r="C204" s="52"/>
     </row>
     <row r="205" ht="15.75" customHeight="1">
-      <c r="A205" s="50"/>
-      <c r="B205" s="50"/>
-      <c r="C205" s="50"/>
+      <c r="A205" s="52"/>
+      <c r="B205" s="52"/>
+      <c r="C205" s="52"/>
     </row>
     <row r="206" ht="15.75" customHeight="1">
-      <c r="A206" s="50"/>
-      <c r="B206" s="50"/>
-      <c r="C206" s="50"/>
+      <c r="A206" s="52"/>
+      <c r="B206" s="52"/>
+      <c r="C206" s="52"/>
     </row>
     <row r="207" ht="15.75" customHeight="1">
-      <c r="A207" s="50"/>
-      <c r="B207" s="50"/>
-      <c r="C207" s="50"/>
+      <c r="A207" s="52"/>
+      <c r="B207" s="52"/>
+      <c r="C207" s="52"/>
     </row>
     <row r="208" ht="15.75" customHeight="1">
-      <c r="A208" s="50"/>
-      <c r="B208" s="50"/>
-      <c r="C208" s="50"/>
+      <c r="A208" s="52"/>
+      <c r="B208" s="52"/>
+      <c r="C208" s="52"/>
     </row>
     <row r="209" ht="15.75" customHeight="1">
-      <c r="A209" s="50"/>
-      <c r="B209" s="50"/>
-      <c r="C209" s="50"/>
+      <c r="A209" s="52"/>
+      <c r="B209" s="52"/>
+      <c r="C209" s="52"/>
     </row>
     <row r="210" ht="15.75" customHeight="1">
-      <c r="A210" s="50"/>
-      <c r="B210" s="50"/>
-      <c r="C210" s="50"/>
+      <c r="A210" s="52"/>
+      <c r="B210" s="52"/>
+      <c r="C210" s="52"/>
     </row>
     <row r="211" ht="15.75" customHeight="1">
-      <c r="A211" s="50"/>
-      <c r="B211" s="50"/>
-      <c r="C211" s="50"/>
+      <c r="A211" s="52"/>
+      <c r="B211" s="52"/>
+      <c r="C211" s="52"/>
     </row>
     <row r="212" ht="15.75" customHeight="1">
-      <c r="A212" s="50"/>
-      <c r="B212" s="50"/>
-      <c r="C212" s="50"/>
+      <c r="A212" s="52"/>
+      <c r="B212" s="52"/>
+      <c r="C212" s="52"/>
     </row>
     <row r="213" ht="15.75" customHeight="1">
-      <c r="A213" s="50"/>
-      <c r="B213" s="50"/>
-      <c r="C213" s="50"/>
+      <c r="A213" s="52"/>
+      <c r="B213" s="52"/>
+      <c r="C213" s="52"/>
     </row>
     <row r="214" ht="15.75" customHeight="1">
-      <c r="A214" s="50"/>
-      <c r="B214" s="50"/>
-      <c r="C214" s="50"/>
+      <c r="A214" s="52"/>
+      <c r="B214" s="52"/>
+      <c r="C214" s="52"/>
     </row>
     <row r="215" ht="15.75" customHeight="1">
-      <c r="A215" s="50"/>
-      <c r="B215" s="50"/>
-      <c r="C215" s="50"/>
+      <c r="A215" s="52"/>
+      <c r="B215" s="52"/>
+      <c r="C215" s="52"/>
     </row>
     <row r="216" ht="15.75" customHeight="1">
-      <c r="A216" s="50"/>
-      <c r="B216" s="50"/>
-      <c r="C216" s="50"/>
+      <c r="A216" s="52"/>
+      <c r="B216" s="52"/>
+      <c r="C216" s="52"/>
     </row>
     <row r="217" ht="15.75" customHeight="1">
-      <c r="A217" s="50"/>
-      <c r="B217" s="50"/>
-      <c r="C217" s="50"/>
+      <c r="A217" s="52"/>
+      <c r="B217" s="52"/>
+      <c r="C217" s="52"/>
     </row>
     <row r="218" ht="15.75" customHeight="1">
-      <c r="A218" s="50"/>
-      <c r="B218" s="50"/>
-      <c r="C218" s="50"/>
+      <c r="A218" s="52"/>
+      <c r="B218" s="52"/>
+      <c r="C218" s="52"/>
     </row>
     <row r="219" ht="15.75" customHeight="1">
-      <c r="A219" s="50"/>
-      <c r="B219" s="50"/>
-      <c r="C219" s="50"/>
+      <c r="A219" s="52"/>
+      <c r="B219" s="52"/>
+      <c r="C219" s="52"/>
     </row>
     <row r="220" ht="15.75" customHeight="1">
-      <c r="A220" s="50"/>
-      <c r="B220" s="50"/>
-      <c r="C220" s="50"/>
+      <c r="A220" s="52"/>
+      <c r="B220" s="52"/>
+      <c r="C220" s="52"/>
     </row>
     <row r="221" ht="15.75" customHeight="1"/>
     <row r="222" ht="15.75" customHeight="1"/>
